--- a/engine/arcc_study/ARCC_Valuation_Model_03092026_public.xlsx
+++ b/engine/arcc_study/ARCC_Valuation_Model_03092026_public.xlsx
@@ -43,7 +43,7 @@
     <numFmt numFmtId="172" formatCode="0.0000"/>
     <numFmt numFmtId="173" formatCode="0.0000%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,9 @@
     </font>
     <font>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <color rgb="006E7B77"/>
     </font>
     <font>
       <color rgb="00008000"/>
@@ -122,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,50 +133,51 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -741,7 +745,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    deducted EGP 150 MILLION on inference, 950 times too much.</t>
+          <t xml:space="preserve">    deducted EGP 150 MILLION on inference, 949 times too much.</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1199,7 @@
         </is>
       </c>
       <c r="D5" s="14">
-        <f>Assumptions!$B$106</f>
+        <f>Assumptions!$B$107</f>
         <v/>
       </c>
     </row>
@@ -1206,7 +1210,7 @@
         </is>
       </c>
       <c r="D6" s="14">
-        <f>Assumptions!$B$107</f>
+        <f>Assumptions!$B$108</f>
         <v/>
       </c>
     </row>
@@ -1217,7 +1221,7 @@
         </is>
       </c>
       <c r="D7" s="14">
-        <f>Assumptions!$B$108</f>
+        <f>Assumptions!$B$109</f>
         <v/>
       </c>
     </row>
@@ -1259,19 +1263,19 @@
         </is>
       </c>
       <c r="B9" s="14">
+        <f>Assumptions!$B$115</f>
+        <v/>
+      </c>
+      <c r="C9" s="14">
         <f>Assumptions!$B$114</f>
         <v/>
       </c>
-      <c r="C9" s="14">
+      <c r="D9" s="14">
         <f>Assumptions!$B$113</f>
         <v/>
       </c>
-      <c r="D9" s="14">
-        <f>Assumptions!$B$112</f>
-        <v/>
-      </c>
       <c r="E9" s="17">
-        <f>D9-Assumptions!$B$131+'Income Statement'!E20+DCF!B8+DCF!B13+DCF!B14-'Income Statement'!E22</f>
+        <f>D9-Assumptions!$B$132+'Income Statement'!E20+DCF!B8+DCF!B13+DCF!B14-'Income Statement'!E22</f>
         <v/>
       </c>
       <c r="F9" s="17">
@@ -1298,7 +1302,7 @@
         </is>
       </c>
       <c r="D10" s="17">
-        <f>Assumptions!$B$109+Assumptions!$B$110+Assumptions!$B$111</f>
+        <f>Assumptions!$B$110+Assumptions!$B$111+Assumptions!$B$112</f>
         <v/>
       </c>
       <c r="E10" s="17">
@@ -1328,35 +1332,35 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="32">
+        <f>Assumptions!$B$105</f>
+        <v/>
+      </c>
+      <c r="C11" s="32">
         <f>Assumptions!$B$104</f>
         <v/>
       </c>
-      <c r="C11" s="31">
+      <c r="D11" s="32">
         <f>Assumptions!$B$103</f>
         <v/>
       </c>
-      <c r="D11" s="31">
-        <f>Assumptions!$B$102</f>
-        <v/>
-      </c>
-      <c r="E11" s="36">
+      <c r="E11" s="37">
         <f>E8+E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="37">
         <f>F8+F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="37">
         <f>G8+G9+G10</f>
         <v/>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="37">
         <f>H8+H9+H10</f>
         <v/>
       </c>
-      <c r="I11" s="36">
+      <c r="I11" s="37">
         <f>I8+I9+I10</f>
         <v/>
       </c>
@@ -1368,11 +1372,11 @@
         </is>
       </c>
       <c r="B12" s="14">
+        <f>Assumptions!$B$126</f>
+        <v/>
+      </c>
+      <c r="C12" s="14">
         <f>Assumptions!$B$125</f>
-        <v/>
-      </c>
-      <c r="C12" s="14">
-        <f>Assumptions!$B$124</f>
         <v/>
       </c>
       <c r="D12" s="14">
@@ -1438,7 +1442,7 @@
         </is>
       </c>
       <c r="D14" s="14">
-        <f>Assumptions!$B$105</f>
+        <f>Assumptions!$B$106</f>
         <v/>
       </c>
       <c r="E14" s="17">
@@ -1468,35 +1472,35 @@
           <t>Equity attributable to owners</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="32">
+        <f>Assumptions!$B$118</f>
+        <v/>
+      </c>
+      <c r="C15" s="32">
         <f>Assumptions!$B$117</f>
         <v/>
       </c>
-      <c r="C15" s="31">
+      <c r="D15" s="32">
         <f>Assumptions!$B$116</f>
         <v/>
       </c>
-      <c r="D15" s="31">
-        <f>Assumptions!$B$115</f>
-        <v/>
-      </c>
-      <c r="E15" s="36">
-        <f>D15-Assumptions!$B$131+'Income Statement'!E20-'Income Statement'!E22</f>
-        <v/>
-      </c>
-      <c r="F15" s="36">
+      <c r="E15" s="37">
+        <f>D15-Assumptions!$B$132+'Income Statement'!E20-'Income Statement'!E22</f>
+        <v/>
+      </c>
+      <c r="F15" s="37">
         <f>E15+'Income Statement'!F20-'Income Statement'!F22</f>
         <v/>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="37">
         <f>F15+'Income Statement'!G20-'Income Statement'!G22</f>
         <v/>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="37">
         <f>G15+'Income Statement'!H20-'Income Statement'!H22</f>
         <v/>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="37">
         <f>H15+'Income Statement'!I20-'Income Statement'!I22</f>
         <v/>
       </c>
@@ -1641,7 +1645,7 @@
         </is>
       </c>
       <c r="B21" s="17">
-        <f>Assumptions!$B$102</f>
+        <f>Assumptions!$B$103</f>
         <v/>
       </c>
     </row>
@@ -1652,7 +1656,7 @@
         </is>
       </c>
       <c r="B22" s="17">
-        <f>-Assumptions!$B$105</f>
+        <f>-Assumptions!$B$106</f>
         <v/>
       </c>
     </row>
@@ -1674,7 +1678,7 @@
         </is>
       </c>
       <c r="B24" s="17">
-        <f>Assumptions!$B$115+Assumptions!$B$118</f>
+        <f>Assumptions!$B$116+Assumptions!$B$119</f>
         <v/>
       </c>
     </row>
@@ -1684,7 +1688,7 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B25" s="44">
+      <c r="B25" s="45">
         <f>B23-B24</f>
         <v/>
       </c>
@@ -1831,7 +1835,7 @@
         </is>
       </c>
       <c r="B6" s="14">
-        <f>Assumptions!$B$82</f>
+        <f>Assumptions!$B$83</f>
         <v/>
       </c>
       <c r="C6" s="14">
@@ -1888,27 +1892,27 @@
           <t>Cash from operations</t>
         </is>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="37">
         <f>B5+B6</f>
         <v/>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="37">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="37">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="37">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="37">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="37">
         <f>G5+G6+G7</f>
         <v/>
       </c>
@@ -1920,7 +1924,7 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>-Assumptions!$B$85</f>
+        <f>-Assumptions!$B$86</f>
         <v/>
       </c>
       <c r="C9" s="14">
@@ -1950,27 +1954,27 @@
           <t>Free cash flow to equity</t>
         </is>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="37">
         <f>B8+B9</f>
         <v/>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="37">
         <f>C8+C9</f>
         <v/>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="37">
         <f>D8+D9</f>
         <v/>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="37">
         <f>E8+E9</f>
         <v/>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="37">
         <f>F8+F9</f>
         <v/>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="37">
         <f>G8+G9</f>
         <v/>
       </c>
@@ -1982,7 +1986,7 @@
         </is>
       </c>
       <c r="B11" s="14">
-        <f>-Assumptions!$B$131</f>
+        <f>-Assumptions!$B$132</f>
         <v/>
       </c>
       <c r="C11" s="17">
@@ -2013,7 +2017,7 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>Assumptions!$B$112</f>
+        <f>Assumptions!$B$113</f>
         <v/>
       </c>
       <c r="C12" s="14">
@@ -2804,7 +2808,7 @@
           <t>Windows scored</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="30" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2844,7 +2848,7 @@
           <t>Cone width against the benchmark</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="31" t="n">
         <v>1.234292255993717</v>
       </c>
     </row>
@@ -2903,7 +2907,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="45" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): explicit-window cost of capital against terminal growth</t>
         </is>
@@ -3038,7 +3042,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): explicit-window rate against TERMINAL rate</t>
         </is>
@@ -3173,7 +3177,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): beta</t>
         </is>
@@ -3230,7 +3234,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="A24" s="46" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): margin shift</t>
         </is>
@@ -3287,7 +3291,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="45" t="inlineStr">
+      <c r="A28" s="46" t="inlineStr">
         <is>
           <t>Fair value per share (EGP): net cash (EGP mn)</t>
         </is>
@@ -3538,35 +3542,35 @@
           <t>Price / earnings (at spot)</t>
         </is>
       </c>
-      <c r="B7" s="39">
+      <c r="B7" s="40">
         <f>Assumptions!$B$5/B5</f>
         <v/>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="40">
         <f>Assumptions!$B$5/C5</f>
         <v/>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="40">
         <f>Assumptions!$B$5/D5</f>
         <v/>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="40">
         <f>Assumptions!$B$5/E5</f>
         <v/>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="40">
         <f>Assumptions!$B$5/F5</f>
         <v/>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="40">
         <f>Assumptions!$B$5/G5</f>
         <v/>
       </c>
-      <c r="H7" s="39">
+      <c r="H7" s="40">
         <f>Assumptions!$B$5/H5</f>
         <v/>
       </c>
-      <c r="I7" s="39">
+      <c r="I7" s="40">
         <f>Assumptions!$B$5/I5</f>
         <v/>
       </c>
@@ -3577,35 +3581,35 @@
           <t>Price / book (at spot)</t>
         </is>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="40">
         <f>Assumptions!$B$5/B6</f>
         <v/>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="40">
         <f>Assumptions!$B$5/C6</f>
         <v/>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="40">
         <f>Assumptions!$B$5/D6</f>
         <v/>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="40">
         <f>Assumptions!$B$5/E6</f>
         <v/>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="40">
         <f>Assumptions!$B$5/F6</f>
         <v/>
       </c>
-      <c r="G8" s="39">
+      <c r="G8" s="40">
         <f>Assumptions!$B$5/G6</f>
         <v/>
       </c>
-      <c r="H8" s="39">
+      <c r="H8" s="40">
         <f>Assumptions!$B$5/H6</f>
         <v/>
       </c>
-      <c r="I8" s="39">
+      <c r="I8" s="40">
         <f>Assumptions!$B$5/I6</f>
         <v/>
       </c>
@@ -3686,35 +3690,35 @@
           <t>Net (cash) / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="40">
         <f>'Balance Sheet'!B16/'Income Statement'!B14</f>
         <v/>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="40">
         <f>'Balance Sheet'!C16/'Income Statement'!C14</f>
         <v/>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="40">
         <f>'Balance Sheet'!D16/'Income Statement'!D14</f>
         <v/>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="40">
         <f>'Balance Sheet'!E16/'Income Statement'!E14</f>
         <v/>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="40">
         <f>'Balance Sheet'!F16/'Income Statement'!F14</f>
         <v/>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="40">
         <f>'Balance Sheet'!G16/'Income Statement'!G14</f>
         <v/>
       </c>
-      <c r="H11" s="39">
+      <c r="H11" s="40">
         <f>'Balance Sheet'!H16/'Income Statement'!H14</f>
         <v/>
       </c>
-      <c r="I11" s="39">
+      <c r="I11" s="40">
         <f>'Balance Sheet'!I16/'Income Statement'!I14</f>
         <v/>
       </c>
@@ -3741,7 +3745,7 @@
           <t>Shares issued (audited note 20)</t>
         </is>
       </c>
-      <c r="B14" s="42">
+      <c r="B14" s="43">
         <f>Assumptions!$B$6</f>
         <v/>
       </c>
@@ -3752,7 +3756,7 @@
           <t>Less treasury shares (audited note 21)</t>
         </is>
       </c>
-      <c r="B15" s="42">
+      <c r="B15" s="43">
         <f>-Assumptions!$B$7</f>
         <v/>
       </c>
@@ -3763,7 +3767,7 @@
           <t>Shares outstanding — ADOPTED</t>
         </is>
       </c>
-      <c r="B16" s="44">
+      <c r="B16" s="45">
         <f>B14+B15</f>
         <v/>
       </c>
@@ -3774,8 +3778,8 @@
           <t>Shares implied by the FY2025 dividend at EGP 5.34 per share</t>
         </is>
       </c>
-      <c r="B17" s="42">
-        <f>Assumptions!$B$131/5.34</f>
+      <c r="B17" s="43">
+        <f>Assumptions!$B$132/5.34</f>
         <v/>
       </c>
     </row>
@@ -3785,7 +3789,7 @@
           <t>Difference</t>
         </is>
       </c>
-      <c r="B18" s="46">
+      <c r="B18" s="47">
         <f>B17/B16-1</f>
         <v/>
       </c>
@@ -3808,7 +3812,7 @@
         </is>
       </c>
       <c r="B20" s="8">
-        <f>Assumptions!$B$133/Assumptions!$B$134-1</f>
+        <f>Assumptions!$B$134/Assumptions!$B$135-1</f>
         <v/>
       </c>
     </row>
@@ -3819,7 +3823,7 @@
         </is>
       </c>
       <c r="B21" s="17">
-        <f>Assumptions!$B$55*Assumptions!$B$133/Assumptions!$B$134</f>
+        <f>Assumptions!$B$56*Assumptions!$B$134/Assumptions!$B$135</f>
         <v/>
       </c>
     </row>
@@ -3852,7 +3856,7 @@
         </is>
       </c>
       <c r="B24" s="8">
-        <f>Assumptions!$B$135/Assumptions!$B$133</f>
+        <f>Assumptions!$B$136/Assumptions!$B$134</f>
         <v/>
       </c>
     </row>
@@ -3874,7 +3878,7 @@
         </is>
       </c>
       <c r="B26" s="17">
-        <f>4*Assumptions!$B$136</f>
+        <f>4*Assumptions!$B$137</f>
         <v/>
       </c>
     </row>
@@ -3907,7 +3911,7 @@
         </is>
       </c>
       <c r="B29" s="17">
-        <f>Assumptions!$B$137-Assumptions!$B$138-Assumptions!$B$149</f>
+        <f>Assumptions!$B$138-Assumptions!$B$139-Assumptions!$B$150</f>
         <v/>
       </c>
     </row>
@@ -4026,22 +4030,22 @@
         </is>
       </c>
       <c r="B5" s="14">
-        <f>Assumptions!$B$55</f>
+        <f>Assumptions!$B$56</f>
         <v/>
       </c>
       <c r="C5" s="14">
-        <f>Assumptions!$B$76</f>
+        <f>Assumptions!$B$77</f>
         <v/>
       </c>
       <c r="D5" s="14">
         <f>DCF!C45</f>
         <v/>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="40">
         <f>D5/C5</f>
         <v/>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="40">
         <f>D5/B5</f>
         <v/>
       </c>
@@ -4057,22 +4061,22 @@
         </is>
       </c>
       <c r="B6" s="14">
-        <f>Assumptions!$B$164</f>
+        <f>Assumptions!$B$167</f>
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>Assumptions!$B$165</f>
+        <f>Assumptions!$B$168</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>Assumptions!$B$166</f>
-        <v/>
-      </c>
-      <c r="E6" s="39">
+        <f>Assumptions!$B$169</f>
+        <v/>
+      </c>
+      <c r="E6" s="40">
         <f>D6/C6</f>
         <v/>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="40">
         <f>D6/B6</f>
         <v/>
       </c>
@@ -4088,22 +4092,22 @@
         </is>
       </c>
       <c r="B7" s="14">
-        <f>Assumptions!$B$167</f>
+        <f>Assumptions!$B$170</f>
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>Assumptions!$B$168</f>
+        <f>Assumptions!$B$171</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>Assumptions!$B$169</f>
-        <v/>
-      </c>
-      <c r="E7" s="39">
+        <f>Assumptions!$B$172</f>
+        <v/>
+      </c>
+      <c r="E7" s="40">
         <f>D7/C7</f>
         <v/>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="40">
         <f>D7/B7</f>
         <v/>
       </c>
@@ -4118,7 +4122,7 @@
           <t>Peer average price / earnings (excluding the subject)</t>
         </is>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="48">
         <f>AVERAGE(E6:E7)</f>
         <v/>
       </c>
@@ -4154,8 +4158,8 @@
           <t>Nameplate capacity (Mt)</t>
         </is>
       </c>
-      <c r="B13" s="48">
-        <f>Assumptions!$B$159</f>
+      <c r="B13" s="49">
+        <f>Assumptions!$B$160</f>
         <v/>
       </c>
     </row>
@@ -4165,8 +4169,8 @@
           <t>Production 2025 (Mt)</t>
         </is>
       </c>
-      <c r="B14" s="48">
-        <f>Assumptions!$B$160</f>
+      <c r="B14" s="49">
+        <f>Assumptions!$B$161</f>
         <v/>
       </c>
     </row>
@@ -4176,19 +4180,37 @@
           <t>Domestic consumption 2025 (Mt)</t>
         </is>
       </c>
-      <c r="B15" s="48">
-        <f>Assumptions!$B$161</f>
+      <c r="B15" s="49">
+        <f>Assumptions!$B$164</f>
+        <v/>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which CEMENT exports (Mt)</t>
+        </is>
+      </c>
+      <c r="D15" s="19">
+        <f>Assumptions!$B$162</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Exports 2025 (Mt)</t>
-        </is>
-      </c>
-      <c r="B16" s="48">
-        <f>Assumptions!$B$162</f>
+          <t>Exports 2025 (Mt) — cement AND clinker</t>
+        </is>
+      </c>
+      <c r="B16" s="49">
+        <f>Assumptions!$B$165</f>
+        <v/>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which CLINKER exports (Mt) — no cement mill involved</t>
+        </is>
+      </c>
+      <c r="D16" s="19">
+        <f>Assumptions!$B$163</f>
         <v/>
       </c>
     </row>
@@ -4198,19 +4220,28 @@
           <t>Dormant capacity under revival (Mt)</t>
         </is>
       </c>
-      <c r="B17" s="48">
-        <f>Assumptions!$B$163</f>
+      <c r="B17" s="49">
+        <f>Assumptions!$B$166</f>
+        <v/>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CEMENT sold 2025 (Mt) — domestic plus cement exports</t>
+        </is>
+      </c>
+      <c r="D17" s="19">
+        <f>B15+D15</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sector utilisation</t>
+          <t>Sector utilisation — CEMENT sold over CEMENT nameplate</t>
         </is>
       </c>
       <c r="B18" s="8">
-        <f>B14/B13</f>
+        <f>D17/B13</f>
         <v/>
       </c>
     </row>
@@ -4221,7 +4252,7 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>Assumptions!$B$13/B13</f>
+        <f>Assumptions!$B$14/B13</f>
         <v/>
       </c>
     </row>
@@ -4244,6 +4275,17 @@
       </c>
       <c r="B21" s="8">
         <f>'Segments'!B18/B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: all product over cement nameplate — RETIRED, the bases do not match</t>
+        </is>
+      </c>
+      <c r="B22" s="8">
+        <f>B14/B13</f>
         <v/>
       </c>
     </row>
@@ -4555,15 +4597,15 @@
         </is>
       </c>
       <c r="B17" s="13">
-        <f>((Assumptions!$B$153-15)*Assumptions!$B$13*Assumptions!$B$11+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>((Assumptions!$B$154-15)*Assumptions!$B$14*Assumptions!$B$12+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="C17" s="13">
-        <f>(Assumptions!$B$153*Assumptions!$B$13*Assumptions!$B$11+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>(Assumptions!$B$154*Assumptions!$B$14*Assumptions!$B$12+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>((Assumptions!$B$153+15)*Assumptions!$B$13*Assumptions!$B$11+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>((Assumptions!$B$154+15)*Assumptions!$B$14*Assumptions!$B$12+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="E17" s="8">
@@ -4578,15 +4620,15 @@
         </is>
       </c>
       <c r="B18" s="13">
-        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$155-1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$156-1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="C18" s="13">
-        <f>('Relative &amp; Normalized'!$B$12*Assumptions!$B$155+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>('Relative &amp; Normalized'!$B$12*Assumptions!$B$156+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$155+1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$156+1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="E18" s="8">
@@ -4706,7 +4748,7 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>Assumptions!$B$13</f>
+        <f>Assumptions!$B$14</f>
         <v/>
       </c>
     </row>
@@ -4717,7 +4759,7 @@
         </is>
       </c>
       <c r="B6" s="17">
-        <f>Assumptions!$B$152</f>
+        <f>Assumptions!$B$153</f>
         <v/>
       </c>
     </row>
@@ -4728,7 +4770,7 @@
         </is>
       </c>
       <c r="B7" s="17">
-        <f>Assumptions!$B$153</f>
+        <f>Assumptions!$B$154</f>
         <v/>
       </c>
     </row>
@@ -4750,7 +4792,7 @@
         </is>
       </c>
       <c r="B9" s="17">
-        <f>B7*B5*Assumptions!$B$11</f>
+        <f>B7*B5*Assumptions!$B$12</f>
         <v/>
       </c>
     </row>
@@ -4805,7 +4847,7 @@
         </is>
       </c>
       <c r="B14" s="19">
-        <f>(Assumptions!$B$5*DCF!$B$43-DCF!B40+Assumptions!$B$118)/Assumptions!$B$13/Assumptions!$B$11</f>
+        <f>(Assumptions!$B$5*DCF!$B$43-DCF!B40+Assumptions!$B$119)/Assumptions!$B$14/Assumptions!$B$12</f>
         <v/>
       </c>
     </row>
@@ -4816,7 +4858,7 @@
         </is>
       </c>
       <c r="B15" s="17">
-        <f>Assumptions!$B$106+Assumptions!$B$107</f>
+        <f>Assumptions!$B$107+Assumptions!$B$108</f>
         <v/>
       </c>
     </row>
@@ -4827,7 +4869,7 @@
         </is>
       </c>
       <c r="B16" s="19">
-        <f>B15/Assumptions!$B$13/Assumptions!$B$11</f>
+        <f>B15/Assumptions!$B$14/Assumptions!$B$12</f>
         <v/>
       </c>
     </row>
@@ -5005,15 +5047,15 @@
         </is>
       </c>
       <c r="B28" s="14">
-        <f>Assumptions!$B$83</f>
+        <f>Assumptions!$B$84</f>
         <v/>
       </c>
       <c r="C28" s="14">
-        <f>Assumptions!$B$84</f>
+        <f>Assumptions!$B$85</f>
         <v/>
       </c>
       <c r="D28" s="14">
-        <f>Assumptions!$B$85</f>
+        <f>Assumptions!$B$86</f>
         <v/>
       </c>
     </row>
@@ -5043,15 +5085,15 @@
         </is>
       </c>
       <c r="B30" s="14">
-        <f>Assumptions!$B$80</f>
+        <f>Assumptions!$B$81</f>
         <v/>
       </c>
       <c r="C30" s="14">
-        <f>Assumptions!$B$81</f>
+        <f>Assumptions!$B$82</f>
         <v/>
       </c>
       <c r="D30" s="14">
-        <f>Assumptions!$B$82</f>
+        <f>Assumptions!$B$83</f>
         <v/>
       </c>
     </row>
@@ -5119,15 +5161,15 @@
         </is>
       </c>
       <c r="B34" s="8">
-        <f>B32/(Assumptions!$B$117+Assumptions!$B$125)</f>
+        <f>B32/(Assumptions!$B$118+Assumptions!$B$126)</f>
         <v/>
       </c>
       <c r="C34" s="8">
-        <f>C32/(Assumptions!$B$116+Assumptions!$B$124)</f>
+        <f>C32/(Assumptions!$B$117+Assumptions!$B$125)</f>
         <v/>
       </c>
       <c r="D34" s="8">
-        <f>D32/(Assumptions!$B$115+DCF!$C$44)</f>
+        <f>D32/(Assumptions!$B$116+DCF!$C$44)</f>
         <v/>
       </c>
     </row>
@@ -5175,10 +5217,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Terminal return on capital, REPLACEMENT-COST basis</t>
+          <t>Terminal return on capital, REPLACEMENT-COST basis — ADOPTED (both legs at the same date)</t>
         </is>
       </c>
       <c r="B38" s="22">
+        <f>DCF!D27</f>
+        <v/>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>RETIRED construction, shown for the record and not used:</t>
+        </is>
+      </c>
+      <c r="E38" s="8">
         <f>DCF!B24</f>
         <v/>
       </c>
@@ -5212,7 +5263,7 @@
         </is>
       </c>
       <c r="B41" s="8">
-        <f>Assumptions!$B$50</f>
+        <f>Assumptions!$B$51</f>
         <v/>
       </c>
     </row>
@@ -5262,7 +5313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J172"/>
+  <dimension ref="A1:J175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -5386,61 +5437,66 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Beta (own-stock weekly regression)</t>
+          <t>Beta — median of same-country PEER regressions (tier 2; the own-stock regression is rejected, see below)</t>
         </is>
       </c>
       <c r="B10" s="26" t="n">
         <v>0.9275220650537075</v>
       </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>peers: 0.815, 0.919, 0.936, 1.030</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t xml:space="preserve">   memo — own-stock weekly regression against the EGX30: REJECTED, not used</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="n">
+        <v>0.6980904117648513</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>R-squared 0.047, standard error 0.228, 253 weekly observations to 2026-07-16. The index explains under a twentieth of this share's movement, which is below the usability floor, so tier 1 is unavailable and the peer median above is adopted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>USD/EGP at the valuation date</t>
         </is>
       </c>
-      <c r="B11" s="27" t="n">
+      <c r="B12" s="28" t="n">
         <v>50.3</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>PLANT — AUDITED NOTE 1</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Cement capacity</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Mt/yr</t>
-        </is>
-      </c>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kiln clinker capacity</t>
-        </is>
-      </c>
-      <c r="B14" s="28" t="n">
-        <v>4.2</v>
+          <t>Cement capacity</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="n">
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -5451,898 +5507,898 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Kiln clinker capacity</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Mt/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Clinker factor</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B16" s="26" t="n">
         <v>0.7329</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>t clinker / t cement</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>EXPORT SPLIT — the one ratio the export leg needs; both prices come OUT</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Export clinker price as a fraction of export cement</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="n">
-        <v>0.65</v>
-      </c>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Average USD/EGP FY2025</t>
-        </is>
-      </c>
-      <c r="B18" s="28" t="n">
-        <v>49.26</v>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>audited note 2.5</t>
-        </is>
+          <t>Export clinker price as a fraction of export cement</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Average USD/EGP FY2025</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>audited note 2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Services revenue as a share of goods revenue</t>
         </is>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B20" s="25" t="n">
         <v>0.06325</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>PATHS — FY2025A then FY2026E to FY2030E</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr"/>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Kiln utilisation  (THE volume driver)</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="C22" s="24" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="D22" s="24" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E22" s="24" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F22" s="24" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="G22" s="24" t="n">
-        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Clinker sold as clinker, share of clinker made</t>
+          <t>Kiln utilisation  (THE volume driver)</t>
         </is>
       </c>
       <c r="B23" s="24" t="n">
-        <v>0.3377</v>
+        <v>0.917</v>
       </c>
       <c r="C23" s="24" t="n">
-        <v>0.33</v>
+        <v>0.92</v>
       </c>
       <c r="D23" s="24" t="n">
-        <v>0.32</v>
+        <v>0.925</v>
       </c>
       <c r="E23" s="24" t="n">
-        <v>0.31</v>
+        <v>0.93</v>
       </c>
       <c r="F23" s="24" t="n">
-        <v>0.305</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="G23" s="24" t="n">
-        <v>0.3</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cement exported, share of cement sold</t>
+          <t>Clinker sold as clinker, share of clinker made</t>
         </is>
       </c>
       <c r="B24" s="24" t="n">
-        <v>0.1772</v>
+        <v>0.3377</v>
       </c>
       <c r="C24" s="24" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="D24" s="24" t="n">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="E24" s="24" t="n">
-        <v>0.175</v>
+        <v>0.31</v>
       </c>
       <c r="F24" s="24" t="n">
-        <v>0.17</v>
+        <v>0.305</v>
       </c>
       <c r="G24" s="24" t="n">
-        <v>0.165</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cement stock draw (Mt)</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="C25" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="26" t="n">
-        <v>0</v>
+          <t>Cement exported, share of cement sold</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D25" s="24" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="F25" s="24" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G25" s="24" t="n">
+        <v>0.165</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Local price index</t>
+          <t>Cement stock draw (Mt)</t>
         </is>
       </c>
       <c r="B26" s="26" t="n">
-        <v>1</v>
+        <v>0.0725</v>
       </c>
       <c r="C26" s="26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="D26" s="26" t="n">
-        <v>1.2096</v>
+        <v>0</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>1.318464</v>
+        <v>0</v>
       </c>
       <c r="F26" s="26" t="n">
-        <v>1.417349</v>
+        <v>0</v>
       </c>
       <c r="G26" s="26" t="n">
-        <v>1.516563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Export price index (USD)</t>
+          <t>Local price index</t>
         </is>
       </c>
       <c r="B27" s="26" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="26" t="n">
-        <v>0.968</v>
+        <v>1.08</v>
       </c>
       <c r="D27" s="26" t="n">
-        <v>0.944</v>
+        <v>1.2096</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>0.927</v>
+        <v>1.318464</v>
       </c>
       <c r="F27" s="26" t="n">
-        <v>0.911</v>
+        <v>1.417349</v>
       </c>
       <c r="G27" s="26" t="n">
-        <v>0.895</v>
+        <v>1.516563</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>USD/EGP path</t>
-        </is>
-      </c>
-      <c r="B28" s="27" t="n">
-        <v>49.26</v>
-      </c>
-      <c r="C28" s="27" t="n">
-        <v>55.11</v>
-      </c>
-      <c r="D28" s="27" t="n">
-        <v>60.22</v>
-      </c>
-      <c r="E28" s="27" t="n">
-        <v>64.04000000000001</v>
-      </c>
-      <c r="F28" s="27" t="n">
-        <v>67.17</v>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>70.11</v>
+          <t>Export price index (USD)</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="26" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="F28" s="26" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="G28" s="26" t="n">
+        <v>0.895</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Local cost-inflation index</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="26" t="n">
-        <v>1.115</v>
-      </c>
-      <c r="D29" s="26" t="n">
-        <v>1.2488</v>
-      </c>
-      <c r="E29" s="26" t="n">
-        <v>1.361192</v>
-      </c>
-      <c r="F29" s="26" t="n">
-        <v>1.463281</v>
-      </c>
-      <c r="G29" s="26" t="n">
-        <v>1.565711</v>
+          <t>USD/EGP path</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="C29" s="28" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="D29" s="28" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="E29" s="28" t="n">
+        <v>64.04000000000001</v>
+      </c>
+      <c r="F29" s="28" t="n">
+        <v>67.17</v>
+      </c>
+      <c r="G29" s="28" t="n">
+        <v>70.11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Local cost-inflation index</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="26" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>1.2488</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>1.361192</v>
+      </c>
+      <c r="F30" s="26" t="n">
+        <v>1.463281</v>
+      </c>
+      <c r="G30" s="26" t="n">
+        <v>1.565711</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Alternative-fuel saving on materials</t>
         </is>
       </c>
-      <c r="B30" s="24" t="n">
+      <c r="B31" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C30" s="24" t="n">
+      <c r="C31" s="24" t="n">
         <v>0.015</v>
       </c>
-      <c r="D30" s="24" t="n">
+      <c r="D31" s="24" t="n">
         <v>0.03</v>
       </c>
-      <c r="E30" s="24" t="n">
+      <c r="E31" s="24" t="n">
         <v>0.04</v>
       </c>
-      <c r="F30" s="24" t="n">
+      <c r="F31" s="24" t="n">
         <v>0.048</v>
       </c>
-      <c r="G30" s="24" t="n">
+      <c r="G31" s="24" t="n">
         <v>0.055</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>FORECAST DRIVERS — FY2026E to FY2030E</t>
         </is>
       </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="15" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="15" t="n"/>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
-      <c r="H31" s="15" t="n"/>
-      <c r="I31" s="15" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr"/>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr"/>
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Depreciation as % of revenue</t>
-        </is>
-      </c>
-      <c r="B33" s="24" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="C33" s="24" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="D33" s="24" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="E33" s="24" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="F33" s="24" t="n">
-        <v>0.033</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EGP marginal cost-of-debt path</t>
+          <t>Depreciation as % of revenue</t>
         </is>
       </c>
       <c r="B34" s="24" t="n">
-        <v>0.206</v>
+        <v>0.025</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>0.181</v>
+        <v>0.027</v>
       </c>
       <c r="D34" s="24" t="n">
-        <v>0.161</v>
+        <v>0.029</v>
       </c>
       <c r="E34" s="24" t="n">
-        <v>0.149</v>
+        <v>0.031</v>
       </c>
       <c r="F34" s="24" t="n">
-        <v>0.14</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Yield earned on cash</t>
+          <t>EGP marginal cost-of-debt path</t>
         </is>
       </c>
       <c r="B35" s="24" t="n">
-        <v>0.15</v>
+        <v>0.206</v>
       </c>
       <c r="C35" s="24" t="n">
-        <v>0.13</v>
+        <v>0.181</v>
       </c>
       <c r="D35" s="24" t="n">
-        <v>0.12</v>
+        <v>0.161</v>
       </c>
       <c r="E35" s="24" t="n">
-        <v>0.112</v>
+        <v>0.149</v>
       </c>
       <c r="F35" s="24" t="n">
-        <v>0.108</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Maintenance capital expenditure</t>
-        </is>
-      </c>
-      <c r="B36" s="28" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>USD/t capacity</t>
-        </is>
+          <t>Yield earned on cash</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C36" s="24" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="D36" s="24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E36" s="24" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="F36" s="24" t="n">
+        <v>0.108</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Change in working capital / change in revenue</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="n">
-        <v>0.12</v>
+          <t>Maintenance capital expenditure</t>
+        </is>
+      </c>
+      <c r="B37" s="29" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>USD/t capacity</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Change in working capital / change in revenue</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Dividend payout ratio</t>
         </is>
       </c>
-      <c r="B38" s="24" t="n">
+      <c r="B39" s="24" t="n">
         <v>0.556</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>COST OF CAPITAL</t>
         </is>
       </c>
-      <c r="B39" s="15" t="n"/>
-      <c r="C39" s="15" t="n"/>
-      <c r="D39" s="15" t="n"/>
-      <c r="E39" s="15" t="n"/>
-      <c r="F39" s="15" t="n"/>
-      <c r="G39" s="15" t="n"/>
-      <c r="H39" s="15" t="n"/>
-      <c r="I39" s="15" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Risk-free rate (EGP 10-year government)</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="n">
-        <v>0.2295</v>
-      </c>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
+      <c r="H40" s="15" t="n"/>
+      <c r="I40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sovereign default spread (netted out)</t>
+          <t>Risk-free rate (EGP 10-year government)</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
-        <v>0.034</v>
+        <v>0.2295</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
+          <t>Sovereign default spread (netted out)</t>
         </is>
       </c>
       <c r="B42" s="25" t="n">
-        <v>0.0941</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Euribor (EBRD and NBE reference rate)</t>
+          <t>Equity risk premium</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
-        <v>0.0249</v>
+        <v>0.0941</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EGP marginal borrowing rate (corridor + 0.6%)</t>
+          <t>Euribor (EBRD and NBE reference rate)</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
-        <v>0.206</v>
+        <v>0.0249</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Expected EGP depreciation against the euro</t>
+          <t>EGP marginal borrowing rate (corridor + 0.6%)</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
-        <v>0.06</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>Expected EGP depreciation against the euro</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
+          <t>Terminal cost of debt</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
+          <t>Terminal risk-free rate</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
-        </is>
-      </c>
-      <c r="B49" s="24" t="n">
-        <v>0.2</v>
+          <t>Terminal equity risk premium</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Terminal growth rate</t>
+          <t>Terminal debt weight</t>
         </is>
       </c>
       <c r="B50" s="24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Terminal growth rate</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Elapsed fraction of FY2026 at the valuation date</t>
         </is>
       </c>
-      <c r="B51" s="26" t="n">
+      <c r="B52" s="26" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>AUDITED INCOME STATEMENT — PASTED CLASS 1 (EGP mn)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="n"/>
-      <c r="C52" s="15" t="n"/>
-      <c r="D52" s="15" t="n"/>
-      <c r="E52" s="15" t="n"/>
-      <c r="F52" s="15" t="n"/>
-      <c r="G52" s="15" t="n"/>
-      <c r="H52" s="15" t="n"/>
-      <c r="I52" s="15" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>FY2023 sales (net)</t>
-        </is>
-      </c>
-      <c r="B53" s="29" t="n">
-        <v>6042.831338</v>
-      </c>
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="15" t="n"/>
+      <c r="F53" s="15" t="n"/>
+      <c r="G53" s="15" t="n"/>
+      <c r="H53" s="15" t="n"/>
+      <c r="I53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FY2024 sales (net)</t>
-        </is>
-      </c>
-      <c r="B54" s="29" t="n">
-        <v>8729.782821000001</v>
+          <t>FY2023 sales (net)</t>
+        </is>
+      </c>
+      <c r="B54" s="30" t="n">
+        <v>6042.831338</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FY2025 sales (net)</t>
-        </is>
-      </c>
-      <c r="B55" s="29" t="n">
-        <v>12447.320081</v>
+          <t>FY2024 sales (net)</t>
+        </is>
+      </c>
+      <c r="B55" s="30" t="n">
+        <v>8729.782821000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FY2023 cost of sales</t>
-        </is>
-      </c>
-      <c r="B56" s="29" t="n">
-        <v>4759.815212</v>
+          <t>FY2025 sales (net)</t>
+        </is>
+      </c>
+      <c r="B56" s="30" t="n">
+        <v>12447.320081</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FY2024 cost of sales</t>
-        </is>
-      </c>
-      <c r="B57" s="29" t="n">
-        <v>6642.972487</v>
+          <t>FY2023 cost of sales</t>
+        </is>
+      </c>
+      <c r="B57" s="30" t="n">
+        <v>4759.815212</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FY2025 cost of sales</t>
-        </is>
-      </c>
-      <c r="B58" s="29" t="n">
-        <v>7389.054416</v>
+          <t>FY2024 cost of sales</t>
+        </is>
+      </c>
+      <c r="B58" s="30" t="n">
+        <v>6642.972487</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FY2023 general and administrative expenses</t>
-        </is>
-      </c>
-      <c r="B59" s="29" t="n">
-        <v>183.940276</v>
+          <t>FY2025 cost of sales</t>
+        </is>
+      </c>
+      <c r="B59" s="30" t="n">
+        <v>7389.054416</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FY2024 general and administrative expenses</t>
-        </is>
-      </c>
-      <c r="B60" s="29" t="n">
-        <v>267.798104</v>
+          <t>FY2023 general and administrative expenses</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="n">
+        <v>183.940276</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FY2025 general and administrative expenses</t>
-        </is>
-      </c>
-      <c r="B61" s="29" t="n">
-        <v>384.332833</v>
+          <t>FY2024 general and administrative expenses</t>
+        </is>
+      </c>
+      <c r="B61" s="30" t="n">
+        <v>267.798104</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FY2023 provisions charged</t>
-        </is>
-      </c>
-      <c r="B62" s="29" t="n">
-        <v>15.220195</v>
+          <t>FY2025 general and administrative expenses</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="n">
+        <v>384.332833</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FY2024 provisions charged</t>
-        </is>
-      </c>
-      <c r="B63" s="29" t="n">
-        <v>56.05295</v>
+          <t>FY2023 provisions charged</t>
+        </is>
+      </c>
+      <c r="B63" s="30" t="n">
+        <v>15.220195</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FY2025 provisions charged</t>
-        </is>
-      </c>
-      <c r="B64" s="29" t="n">
-        <v>74.505707</v>
+          <t>FY2024 provisions charged</t>
+        </is>
+      </c>
+      <c r="B64" s="30" t="n">
+        <v>56.05295</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FY2023 expected credit losses</t>
-        </is>
-      </c>
-      <c r="B65" s="29" t="n">
-        <v>4.745753</v>
+          <t>FY2025 provisions charged</t>
+        </is>
+      </c>
+      <c r="B65" s="30" t="n">
+        <v>74.505707</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FY2024 expected credit losses</t>
-        </is>
-      </c>
-      <c r="B66" s="29" t="n">
-        <v>-1.106452</v>
+          <t>FY2023 expected credit losses</t>
+        </is>
+      </c>
+      <c r="B66" s="30" t="n">
+        <v>4.745753</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FY2025 expected credit losses</t>
-        </is>
-      </c>
-      <c r="B67" s="29" t="n">
-        <v>3.603563</v>
+          <t>FY2024 expected credit losses</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="n">
+        <v>-1.106452</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FY2023 profit before tax</t>
-        </is>
-      </c>
-      <c r="B68" s="29" t="n">
-        <v>930.231432</v>
+          <t>FY2025 expected credit losses</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="n">
+        <v>3.603563</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FY2024 profit before tax</t>
-        </is>
-      </c>
-      <c r="B69" s="29" t="n">
-        <v>1505.866118</v>
+          <t>FY2023 profit before tax</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="n">
+        <v>930.231432</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FY2025 profit before tax</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="n">
-        <v>4725.157878</v>
+          <t>FY2024 profit before tax</t>
+        </is>
+      </c>
+      <c r="B70" s="30" t="n">
+        <v>1505.866118</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FY2023 income tax</t>
-        </is>
-      </c>
-      <c r="B71" s="29" t="n">
-        <v>232.732802</v>
+          <t>FY2025 profit before tax</t>
+        </is>
+      </c>
+      <c r="B71" s="30" t="n">
+        <v>4725.157878</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FY2024 income tax</t>
-        </is>
-      </c>
-      <c r="B72" s="29" t="n">
-        <v>345.730996</v>
+          <t>FY2023 income tax</t>
+        </is>
+      </c>
+      <c r="B72" s="30" t="n">
+        <v>232.732802</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FY2025 income tax</t>
-        </is>
-      </c>
-      <c r="B73" s="29" t="n">
-        <v>1125.467657</v>
+          <t>FY2024 income tax</t>
+        </is>
+      </c>
+      <c r="B73" s="30" t="n">
+        <v>345.730996</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FY2023 attributable profit</t>
-        </is>
-      </c>
-      <c r="B74" s="29" t="n">
-        <v>697.488741</v>
+          <t>FY2025 income tax</t>
+        </is>
+      </c>
+      <c r="B74" s="30" t="n">
+        <v>1125.467657</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FY2024 attributable profit</t>
-        </is>
-      </c>
-      <c r="B75" s="29" t="n">
-        <v>1160.129411</v>
+          <t>FY2023 attributable profit</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="n">
+        <v>697.488741</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FY2025 attributable profit</t>
-        </is>
-      </c>
-      <c r="B76" s="29" t="n">
-        <v>3599.585937</v>
+          <t>FY2024 attributable profit</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="n">
+        <v>1160.129411</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FY2023 earnings per share</t>
-        </is>
-      </c>
-      <c r="B77" s="21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
+          <t>FY2025 attributable profit</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="n">
+        <v>3599.585937</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FY2024 earnings per share</t>
+          <t>FY2023 earnings per share</t>
         </is>
       </c>
       <c r="B78" s="21" t="n">
-        <v>3.02</v>
+        <v>1.81</v>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
@@ -6353,11 +6409,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FY2025 earnings per share</t>
+          <t>FY2024 earnings per share</t>
         </is>
       </c>
       <c r="B79" s="21" t="n">
-        <v>9.49</v>
+        <v>3.02</v>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
@@ -6368,771 +6424,771 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FY2023 depreciation and amortisation</t>
-        </is>
-      </c>
-      <c r="B80" s="29" t="n">
-        <v>250.424521</v>
+          <t>FY2025 earnings per share</t>
+        </is>
+      </c>
+      <c r="B80" s="21" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FY2024 depreciation and amortisation</t>
-        </is>
-      </c>
-      <c r="B81" s="29" t="n">
-        <v>256.801527</v>
+          <t>FY2023 depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B81" s="30" t="n">
+        <v>250.424521</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FY2025 depreciation and amortisation</t>
-        </is>
-      </c>
-      <c r="B82" s="29" t="n">
-        <v>289.771295</v>
+          <t>FY2024 depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B82" s="30" t="n">
+        <v>256.801527</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FY2023 capital expenditure</t>
-        </is>
-      </c>
-      <c r="B83" s="29" t="n">
-        <v>58.543963</v>
+          <t>FY2025 depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B83" s="30" t="n">
+        <v>289.771295</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FY2024 capital expenditure</t>
-        </is>
-      </c>
-      <c r="B84" s="29" t="n">
-        <v>912.0154</v>
+          <t>FY2023 capital expenditure</t>
+        </is>
+      </c>
+      <c r="B84" s="30" t="n">
+        <v>58.543963</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FY2025 capital expenditure</t>
-        </is>
-      </c>
-      <c r="B85" s="29" t="n">
-        <v>796.47076</v>
+          <t>FY2024 capital expenditure</t>
+        </is>
+      </c>
+      <c r="B85" s="30" t="n">
+        <v>912.0154</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FY2025 interest income</t>
-        </is>
-      </c>
-      <c r="B86" s="29" t="n">
-        <v>226.274781</v>
+          <t>FY2025 capital expenditure</t>
+        </is>
+      </c>
+      <c r="B86" s="30" t="n">
+        <v>796.47076</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FY2025 other income</t>
-        </is>
-      </c>
-      <c r="B87" s="29" t="n">
-        <v>53.339508</v>
+          <t>FY2025 interest income</t>
+        </is>
+      </c>
+      <c r="B87" s="30" t="n">
+        <v>226.274781</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FY2025 finance costs</t>
-        </is>
-      </c>
-      <c r="B88" s="29" t="n">
-        <v>49.841733</v>
+          <t>FY2025 other income</t>
+        </is>
+      </c>
+      <c r="B88" s="30" t="n">
+        <v>53.339508</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>FY2025 finance costs</t>
+        </is>
+      </c>
+      <c r="B89" s="30" t="n">
+        <v>49.841733</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>FY2025 foreign exchange differences</t>
         </is>
       </c>
-      <c r="B89" s="29" t="n">
+      <c r="B90" s="30" t="n">
         <v>-101.57824</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="15" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
         <is>
           <t>AUDITED REVENUE AND COST NOTES (EGP mn)</t>
         </is>
       </c>
-      <c r="B90" s="15" t="n"/>
-      <c r="C90" s="15" t="n"/>
-      <c r="D90" s="15" t="n"/>
-      <c r="E90" s="15" t="n"/>
-      <c r="F90" s="15" t="n"/>
-      <c r="G90" s="15" t="n"/>
-      <c r="H90" s="15" t="n"/>
-      <c r="I90" s="15" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>FY2025 local sales of goods</t>
-        </is>
-      </c>
-      <c r="B91" s="29" t="n">
-        <v>8350.454610000001</v>
-      </c>
+      <c r="B91" s="15" t="n"/>
+      <c r="C91" s="15" t="n"/>
+      <c r="D91" s="15" t="n"/>
+      <c r="E91" s="15" t="n"/>
+      <c r="F91" s="15" t="n"/>
+      <c r="G91" s="15" t="n"/>
+      <c r="H91" s="15" t="n"/>
+      <c r="I91" s="15" t="n"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FY2025 local services</t>
-        </is>
-      </c>
-      <c r="B92" s="29" t="n">
-        <v>281.863546</v>
+          <t>FY2025 local sales of goods</t>
+        </is>
+      </c>
+      <c r="B92" s="30" t="n">
+        <v>8350.454610000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FY2025 export sales of goods</t>
-        </is>
-      </c>
-      <c r="B93" s="29" t="n">
-        <v>3356.422381</v>
+          <t>FY2025 local services</t>
+        </is>
+      </c>
+      <c r="B93" s="30" t="n">
+        <v>281.863546</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FY2025 export services</t>
-        </is>
-      </c>
-      <c r="B94" s="29" t="n">
-        <v>458.579544</v>
+          <t>FY2025 export sales of goods</t>
+        </is>
+      </c>
+      <c r="B94" s="30" t="n">
+        <v>3356.422381</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FY2024 total local sales</t>
-        </is>
-      </c>
-      <c r="B95" s="29" t="n">
-        <v>4883.304477</v>
+          <t>FY2025 export services</t>
+        </is>
+      </c>
+      <c r="B95" s="30" t="n">
+        <v>458.579544</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FY2024 total export sales</t>
-        </is>
-      </c>
-      <c r="B96" s="29" t="n">
-        <v>3846.478344</v>
+          <t>FY2024 total local sales</t>
+        </is>
+      </c>
+      <c r="B96" s="30" t="n">
+        <v>4883.304477</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FY2025 cost of sales — materials and fuel</t>
-        </is>
-      </c>
-      <c r="B97" s="29" t="n">
-        <v>5698.184715</v>
+          <t>FY2024 total export sales</t>
+        </is>
+      </c>
+      <c r="B97" s="30" t="n">
+        <v>3846.478344</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FY2025 cost of sales — transportation</t>
-        </is>
-      </c>
-      <c r="B98" s="29" t="n">
-        <v>764.279332</v>
+          <t>FY2025 cost of sales — materials and fuel</t>
+        </is>
+      </c>
+      <c r="B98" s="30" t="n">
+        <v>5698.184715</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FY2025 cost of sales — overheads</t>
-        </is>
-      </c>
-      <c r="B99" s="29" t="n">
-        <v>641.143208</v>
+          <t>FY2025 cost of sales — transportation</t>
+        </is>
+      </c>
+      <c r="B99" s="30" t="n">
+        <v>764.279332</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>FY2025 cost of sales — overheads</t>
+        </is>
+      </c>
+      <c r="B100" s="30" t="n">
+        <v>641.143208</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>FY2025 administrative depreciation</t>
         </is>
       </c>
-      <c r="B100" s="29" t="n">
+      <c r="B101" s="30" t="n">
         <v>4.324134</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="15" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="15" t="inlineStr">
         <is>
           <t>AUDITED BALANCE SHEET — PASTED CLASS 1 (EGP mn)</t>
         </is>
       </c>
-      <c r="B101" s="15" t="n"/>
-      <c r="C101" s="15" t="n"/>
-      <c r="D101" s="15" t="n"/>
-      <c r="E101" s="15" t="n"/>
-      <c r="F101" s="15" t="n"/>
-      <c r="G101" s="15" t="n"/>
-      <c r="H101" s="15" t="n"/>
-      <c r="I101" s="15" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Total assets FY2025</t>
-        </is>
-      </c>
-      <c r="B102" s="29" t="n">
-        <v>8783.721849</v>
-      </c>
+      <c r="B102" s="15" t="n"/>
+      <c r="C102" s="15" t="n"/>
+      <c r="D102" s="15" t="n"/>
+      <c r="E102" s="15" t="n"/>
+      <c r="F102" s="15" t="n"/>
+      <c r="G102" s="15" t="n"/>
+      <c r="H102" s="15" t="n"/>
+      <c r="I102" s="15" t="n"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Total assets FY2024</t>
-        </is>
-      </c>
-      <c r="B103" s="29" t="n">
-        <v>5848.616103</v>
+          <t>Total assets FY2025</t>
+        </is>
+      </c>
+      <c r="B103" s="30" t="n">
+        <v>8783.721849</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Total assets FY2023</t>
-        </is>
-      </c>
-      <c r="B104" s="29" t="n">
-        <v>3887.527427</v>
+          <t>Total assets FY2024</t>
+        </is>
+      </c>
+      <c r="B104" s="30" t="n">
+        <v>5848.616103</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Total liabilities FY2025</t>
-        </is>
-      </c>
-      <c r="B105" s="29" t="n">
-        <v>4140.989609</v>
+          <t>Total assets FY2023</t>
+        </is>
+      </c>
+      <c r="B105" s="30" t="n">
+        <v>3887.527427</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Property, plant and equipment FY2025</t>
-        </is>
-      </c>
-      <c r="B106" s="29" t="n">
-        <v>2522.323523</v>
+          <t>Total liabilities FY2025</t>
+        </is>
+      </c>
+      <c r="B106" s="30" t="n">
+        <v>4140.989609</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Assets under construction FY2025</t>
-        </is>
-      </c>
-      <c r="B107" s="29" t="n">
-        <v>391.543753</v>
+          <t>Property, plant and equipment FY2025</t>
+        </is>
+      </c>
+      <c r="B107" s="30" t="n">
+        <v>2522.323523</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Intangible assets FY2025</t>
-        </is>
-      </c>
-      <c r="B108" s="29" t="n">
-        <v>106.799617</v>
+          <t>Assets under construction FY2025</t>
+        </is>
+      </c>
+      <c r="B108" s="30" t="n">
+        <v>391.543753</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Inventories FY2025</t>
-        </is>
-      </c>
-      <c r="B109" s="29" t="n">
-        <v>1053.646218</v>
+          <t>Intangible assets FY2025</t>
+        </is>
+      </c>
+      <c r="B109" s="30" t="n">
+        <v>106.799617</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Trade receivables FY2025</t>
-        </is>
-      </c>
-      <c r="B110" s="29" t="n">
-        <v>244.416417</v>
+          <t>Inventories FY2025</t>
+        </is>
+      </c>
+      <c r="B110" s="30" t="n">
+        <v>1053.646218</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Debtors and other debit balances FY2025</t>
-        </is>
-      </c>
-      <c r="B111" s="29" t="n">
-        <v>1004.779062</v>
+          <t>Trade receivables FY2025</t>
+        </is>
+      </c>
+      <c r="B111" s="30" t="n">
+        <v>244.416417</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Cash and bank balances FY2025</t>
-        </is>
-      </c>
-      <c r="B112" s="29" t="n">
-        <v>3459.391229</v>
+          <t>Debtors and other debit balances FY2025</t>
+        </is>
+      </c>
+      <c r="B112" s="30" t="n">
+        <v>1004.779062</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cash and bank balances FY2024</t>
-        </is>
-      </c>
-      <c r="B113" s="29" t="n">
-        <v>1687.062873</v>
+          <t>Cash and bank balances FY2025</t>
+        </is>
+      </c>
+      <c r="B113" s="30" t="n">
+        <v>3459.391229</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cash and bank balances FY2023</t>
-        </is>
-      </c>
-      <c r="B114" s="29" t="n">
-        <v>561.09968</v>
+          <t>Cash and bank balances FY2024</t>
+        </is>
+      </c>
+      <c r="B114" s="30" t="n">
+        <v>1687.062873</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Equity attributable to owners FY2025</t>
-        </is>
-      </c>
-      <c r="B115" s="29" t="n">
-        <v>4642.574235</v>
+          <t>Cash and bank balances FY2023</t>
+        </is>
+      </c>
+      <c r="B115" s="30" t="n">
+        <v>561.09968</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Equity attributable to owners FY2024</t>
-        </is>
-      </c>
-      <c r="B116" s="29" t="n">
-        <v>2303.472299</v>
+          <t>Equity attributable to owners FY2025</t>
+        </is>
+      </c>
+      <c r="B116" s="30" t="n">
+        <v>4642.574235</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Equity attributable to owners FY2023</t>
-        </is>
-      </c>
-      <c r="B117" s="29" t="n">
-        <v>1754.221659</v>
+          <t>Equity attributable to owners FY2024</t>
+        </is>
+      </c>
+      <c r="B117" s="30" t="n">
+        <v>2303.472299</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>Equity attributable to owners FY2023</t>
+        </is>
+      </c>
+      <c r="B118" s="30" t="n">
+        <v>1754.221659</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>Non-controlling interests FY2025</t>
         </is>
       </c>
-      <c r="B118" s="23" t="n">
+      <c r="B119" s="23" t="n">
         <v>0.158005</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="15" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="15" t="inlineStr">
         <is>
           <t>AUDITED DEBT NOTE 25 (EGP mn)</t>
         </is>
       </c>
-      <c r="B119" s="15" t="n"/>
-      <c r="C119" s="15" t="n"/>
-      <c r="D119" s="15" t="n"/>
-      <c r="E119" s="15" t="n"/>
-      <c r="F119" s="15" t="n"/>
-      <c r="G119" s="15" t="n"/>
-      <c r="H119" s="15" t="n"/>
-      <c r="I119" s="15" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>CIB credit facilities — EGP</t>
-        </is>
-      </c>
-      <c r="B120" s="29" t="n">
-        <v>99.916937</v>
-      </c>
+      <c r="B120" s="15" t="n"/>
+      <c r="C120" s="15" t="n"/>
+      <c r="D120" s="15" t="n"/>
+      <c r="E120" s="15" t="n"/>
+      <c r="F120" s="15" t="n"/>
+      <c r="G120" s="15" t="n"/>
+      <c r="H120" s="15" t="n"/>
+      <c r="I120" s="15" t="n"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>National Bank of Egypt facility — EUR</t>
-        </is>
-      </c>
-      <c r="B121" s="29" t="n">
-        <v>145.741484</v>
+          <t>CIB credit facilities — EGP</t>
+        </is>
+      </c>
+      <c r="B121" s="30" t="n">
+        <v>99.916937</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EBRD facility — EUR</t>
-        </is>
-      </c>
-      <c r="B122" s="29" t="n">
-        <v>888.274195</v>
+          <t>National Bank of Egypt facility — EUR</t>
+        </is>
+      </c>
+      <c r="B122" s="30" t="n">
+        <v>145.741484</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Lease liabilities</t>
-        </is>
-      </c>
-      <c r="B123" s="29" t="n">
-        <v>1.176042</v>
+          <t>EBRD facility — EUR</t>
+        </is>
+      </c>
+      <c r="B123" s="30" t="n">
+        <v>888.274195</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Total interest-bearing debt FY2024</t>
-        </is>
-      </c>
-      <c r="B124" s="29" t="n">
-        <v>760.917684</v>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="B124" s="30" t="n">
+        <v>1.176042</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Total interest-bearing debt FY2023</t>
-        </is>
-      </c>
-      <c r="B125" s="29" t="n">
-        <v>90.07427300000001</v>
+          <t>Total interest-bearing debt FY2024</t>
+        </is>
+      </c>
+      <c r="B125" s="30" t="n">
+        <v>760.917684</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FY2025 loan interest expense</t>
-        </is>
-      </c>
-      <c r="B126" s="29" t="n">
-        <v>24.61313</v>
+          <t>Total interest-bearing debt FY2023</t>
+        </is>
+      </c>
+      <c r="B126" s="30" t="n">
+        <v>90.07427300000001</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FY2025 credit-facility interest expense</t>
-        </is>
-      </c>
-      <c r="B127" s="29" t="n">
-        <v>23.00737</v>
+          <t>FY2025 loan interest expense</t>
+        </is>
+      </c>
+      <c r="B127" s="30" t="n">
+        <v>24.61313</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FY2024 loan interest expense</t>
-        </is>
-      </c>
-      <c r="B128" s="29" t="n">
-        <v>2.754107</v>
+          <t>FY2025 credit-facility interest expense</t>
+        </is>
+      </c>
+      <c r="B128" s="30" t="n">
+        <v>23.00737</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>FY2024 loan interest expense</t>
+        </is>
+      </c>
+      <c r="B129" s="30" t="n">
+        <v>2.754107</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
           <t>FY2024 credit-facility interest expense</t>
         </is>
       </c>
-      <c r="B129" s="29" t="n">
+      <c r="B130" s="30" t="n">
         <v>85.95302599999999</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="15" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="15" t="inlineStr">
         <is>
           <t>DIVIDENDS AND Q1-2026 (EGP mn)</t>
         </is>
       </c>
-      <c r="B130" s="15" t="n"/>
-      <c r="C130" s="15" t="n"/>
-      <c r="D130" s="15" t="n"/>
-      <c r="E130" s="15" t="n"/>
-      <c r="F130" s="15" t="n"/>
-      <c r="G130" s="15" t="n"/>
-      <c r="H130" s="15" t="n"/>
-      <c r="I130" s="15" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>FY2025 dividend declared</t>
-        </is>
-      </c>
-      <c r="B131" s="29" t="n">
-        <v>2001.79216</v>
-      </c>
+      <c r="B131" s="15" t="n"/>
+      <c r="C131" s="15" t="n"/>
+      <c r="D131" s="15" t="n"/>
+      <c r="E131" s="15" t="n"/>
+      <c r="F131" s="15" t="n"/>
+      <c r="G131" s="15" t="n"/>
+      <c r="H131" s="15" t="n"/>
+      <c r="I131" s="15" t="n"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FY2024 dividend approved and paid</t>
-        </is>
-      </c>
-      <c r="B132" s="29" t="n">
-        <v>1102.110289</v>
+          <t>FY2025 dividend declared</t>
+        </is>
+      </c>
+      <c r="B132" s="30" t="n">
+        <v>2001.79216</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Q1-2026 sales</t>
-        </is>
-      </c>
-      <c r="B133" s="29" t="n">
-        <v>2995.95935</v>
+          <t>FY2024 dividend approved and paid</t>
+        </is>
+      </c>
+      <c r="B133" s="30" t="n">
+        <v>1102.110289</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Q1-2025 sales</t>
-        </is>
-      </c>
-      <c r="B134" s="29" t="n">
-        <v>2554.448091</v>
+          <t>Q1-2026 sales</t>
+        </is>
+      </c>
+      <c r="B134" s="30" t="n">
+        <v>2995.95935</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Q1-2026 gross profit</t>
-        </is>
-      </c>
-      <c r="B135" s="29" t="n">
-        <v>1286.145881</v>
+          <t>Q1-2025 sales</t>
+        </is>
+      </c>
+      <c r="B135" s="30" t="n">
+        <v>2554.448091</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Q1-2026 attributable profit</t>
-        </is>
-      </c>
-      <c r="B136" s="29" t="n">
-        <v>943.068309</v>
+          <t>Q1-2026 gross profit</t>
+        </is>
+      </c>
+      <c r="B136" s="30" t="n">
+        <v>1286.145881</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Q1-2026 cash and bank balances</t>
-        </is>
-      </c>
-      <c r="B137" s="29" t="n">
-        <v>4379.627379</v>
+          <t>Q1-2026 attributable profit</t>
+        </is>
+      </c>
+      <c r="B137" s="30" t="n">
+        <v>943.068309</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Q1-2026 interest-bearing debt</t>
-        </is>
-      </c>
-      <c r="B138" s="29" t="n">
-        <v>1260.509089</v>
+          <t>Q1-2026 cash and bank balances</t>
+        </is>
+      </c>
+      <c r="B138" s="30" t="n">
+        <v>4379.627379</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Cash and bank balances, reviewed 30 June 2026</t>
-        </is>
-      </c>
-      <c r="B139" s="29" t="n">
-        <v>1970.50114</v>
+          <t>Q1-2026 interest-bearing debt</t>
+        </is>
+      </c>
+      <c r="B139" s="30" t="n">
+        <v>1260.509089</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Interest-bearing debt, reviewed 30 June 2026</t>
-        </is>
-      </c>
-      <c r="B140" s="29" t="n">
-        <v>1283.288394</v>
+          <t>Cash and bank balances, reviewed 30 June 2026</t>
+        </is>
+      </c>
+      <c r="B140" s="30" t="n">
+        <v>1970.50114</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Non-controlling interests, reviewed 30 June 2026</t>
-        </is>
-      </c>
-      <c r="B141" s="23" t="n">
-        <v>0.216054</v>
+          <t>Interest-bearing debt, reviewed 30 June 2026</t>
+        </is>
+      </c>
+      <c r="B141" s="30" t="n">
+        <v>1283.288394</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FY2026+ local price calibration on the H1-2026 reviewed half</t>
+          <t>Non-controlling interests, reviewed 30 June 2026</t>
         </is>
       </c>
       <c r="B142" s="23" t="n">
-        <v>1.078760449086537</v>
+        <v>0.216054</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FY2026+ export price calibration on the H1-2026 reviewed half</t>
+          <t>FY2026+ local price calibration on the H1-2026 reviewed half</t>
         </is>
       </c>
       <c r="B143" s="23" t="n">
-        <v>0.8711327338803936</v>
+        <v>1.078760449086537</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FY2026+ cash-cost calibration on the SAME half</t>
+          <t>FY2026+ export price calibration on the H1-2026 reviewed half</t>
         </is>
       </c>
       <c r="B144" s="23" t="n">
-        <v>0.9763641792055924</v>
+        <v>0.8711327338803936</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Services as a share of goods revenue, recalibrated on the half</t>
+          <t>FY2026+ cash-cost calibration on the SAME half</t>
         </is>
       </c>
       <c r="B145" s="23" t="n">
-        <v>0.0442178203915956</v>
+        <v>0.9763641792055924</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Depreciation correction from this name's own fundamental walk-forward</t>
+          <t>Services as a share of goods revenue, recalibrated on the half</t>
         </is>
       </c>
       <c r="B146" s="23" t="n">
-        <v>1.0298</v>
+        <v>0.0442178203915956</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Export subsidy as a share of export revenue, FY2025 DISCLOSED rate</t>
+          <t>Depreciation correction from this name's own fundamental walk-forward</t>
         </is>
       </c>
       <c r="B147" s="23" t="n">
-        <v>0.008556374712707386</v>
+        <v>1.0298</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Other income excluding the export subsidy, FY2025</t>
-        </is>
-      </c>
-      <c r="B148" s="26" t="n">
-        <v>20.696922</v>
+          <t>Export subsidy as a share of export revenue, FY2025 DISCLOSED rate</t>
+        </is>
+      </c>
+      <c r="B148" s="23" t="n">
+        <v>0.008556374712707386</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Q1-2026 dividends payable</t>
-        </is>
-      </c>
-      <c r="B149" s="29" t="n">
-        <v>2001.79216</v>
+          <t>Other income excluding the export subsidy, FY2025</t>
+        </is>
+      </c>
+      <c r="B149" s="26" t="n">
+        <v>20.696922</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
+          <t>Q1-2026 dividends payable</t>
+        </is>
+      </c>
+      <c r="B150" s="30" t="n">
+        <v>2001.79216</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
           <t>Q1-2026 finance costs</t>
         </is>
       </c>
-      <c r="B150" s="29" t="n">
+      <c r="B151" s="30" t="n">
         <v>11.168843</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="15" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="15" t="inlineStr">
         <is>
           <t>LENS INPUTS</t>
         </is>
       </c>
-      <c r="B151" s="15" t="n"/>
-      <c r="C151" s="15" t="n"/>
-      <c r="D151" s="15" t="n"/>
-      <c r="E151" s="15" t="n"/>
-      <c r="F151" s="15" t="n"/>
-      <c r="G151" s="15" t="n"/>
-      <c r="H151" s="15" t="n"/>
-      <c r="I151" s="15" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Replacement cost per annual tonne</t>
-        </is>
-      </c>
-      <c r="B152" s="29" t="n">
-        <v>130</v>
-      </c>
-      <c r="C152" s="5" t="inlineStr">
-        <is>
-          <t>USD/t</t>
-        </is>
-      </c>
+      <c r="B152" s="15" t="n"/>
+      <c r="C152" s="15" t="n"/>
+      <c r="D152" s="15" t="n"/>
+      <c r="E152" s="15" t="n"/>
+      <c r="F152" s="15" t="n"/>
+      <c r="G152" s="15" t="n"/>
+      <c r="H152" s="15" t="n"/>
+      <c r="I152" s="15" t="n"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Justified enterprise value per annual tonne</t>
-        </is>
-      </c>
-      <c r="B153" s="29" t="n">
-        <v>95</v>
+          <t>Replacement cost per annual tonne</t>
+        </is>
+      </c>
+      <c r="B153" s="30" t="n">
+        <v>130</v>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
@@ -7143,81 +7199,81 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
+          <t>Justified enterprise value per annual tonne</t>
         </is>
       </c>
       <c r="B154" s="30" t="n">
-        <v>4.5</v>
+        <v>95</v>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="B155" s="30" t="n">
-        <v>7</v>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B155" s="31" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA margin</t>
-        </is>
-      </c>
-      <c r="B156" s="24" t="n">
-        <v>0.312</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="B156" s="31" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>Mid-cycle EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B157" s="24" t="n">
+        <v>0.312</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>Normalised revenue haircut</t>
         </is>
       </c>
-      <c r="B157" s="24" t="n">
+      <c r="B158" s="24" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="15" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="15" t="inlineStr">
         <is>
           <t>SECTOR AND PEERS</t>
         </is>
       </c>
-      <c r="B158" s="15" t="n"/>
-      <c r="C158" s="15" t="n"/>
-      <c r="D158" s="15" t="n"/>
-      <c r="E158" s="15" t="n"/>
-      <c r="F158" s="15" t="n"/>
-      <c r="G158" s="15" t="n"/>
-      <c r="H158" s="15" t="n"/>
-      <c r="I158" s="15" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Egyptian nameplate capacity</t>
-        </is>
-      </c>
-      <c r="B159" s="27" t="n">
-        <v>76</v>
-      </c>
-      <c r="C159" s="5" t="inlineStr">
-        <is>
-          <t>Mt</t>
-        </is>
-      </c>
+      <c r="B159" s="15" t="n"/>
+      <c r="C159" s="15" t="n"/>
+      <c r="D159" s="15" t="n"/>
+      <c r="E159" s="15" t="n"/>
+      <c r="F159" s="15" t="n"/>
+      <c r="G159" s="15" t="n"/>
+      <c r="H159" s="15" t="n"/>
+      <c r="I159" s="15" t="n"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Egyptian production 2025</t>
-        </is>
-      </c>
-      <c r="B160" s="27" t="n">
-        <v>72.59999999999999</v>
+          <t>Egyptian nameplate capacity</t>
+        </is>
+      </c>
+      <c r="B160" s="28" t="n">
+        <v>76</v>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
@@ -7228,11 +7284,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Egyptian consumption 2025</t>
-        </is>
-      </c>
-      <c r="B161" s="27" t="n">
-        <v>53.9</v>
+          <t>Egyptian sales 2025 — cement AND clinker</t>
+        </is>
+      </c>
+      <c r="B161" s="28" t="n">
+        <v>72.62479999999999</v>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
@@ -7243,11 +7299,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Egyptian exports 2025</t>
-        </is>
-      </c>
-      <c r="B162" s="27" t="n">
-        <v>18.6</v>
+          <t xml:space="preserve">  of which cement exports</t>
+        </is>
+      </c>
+      <c r="B162" s="28" t="n">
+        <v>11.063</v>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
@@ -7258,87 +7314,132 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Dormant capacity under revival</t>
-        </is>
-      </c>
-      <c r="B163" s="27" t="n">
-        <v>12.6</v>
+          <t xml:space="preserve">  of which clinker exports</t>
+        </is>
+      </c>
+      <c r="B163" s="28" t="n">
+        <v>7.5689</v>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Mt</t>
+          <t>Mt — leaves at the kiln, so it is OUT of the cement utilisation ratio</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Peer — Sinai Cement revenue</t>
-        </is>
-      </c>
-      <c r="B164" s="29" t="n">
-        <v>9090</v>
+          <t>Egyptian consumption 2025</t>
+        </is>
+      </c>
+      <c r="B164" s="28" t="n">
+        <v>53.9929</v>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Peer — Sinai Cement profit</t>
-        </is>
-      </c>
-      <c r="B165" s="29" t="n">
-        <v>2290</v>
+          <t>Egyptian exports 2025</t>
+        </is>
+      </c>
+      <c r="B165" s="28" t="n">
+        <v>18.6319</v>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Peer — Sinai Cement market capitalisation</t>
-        </is>
-      </c>
-      <c r="B166" s="29" t="n">
-        <v>20604.19</v>
+          <t>Dormant capacity under revival</t>
+        </is>
+      </c>
+      <c r="B166" s="28" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Peer — Misr Beni Suef revenue</t>
-        </is>
-      </c>
-      <c r="B167" s="29" t="n">
-        <v>5700</v>
+          <t>Peer — Sinai Cement revenue</t>
+        </is>
+      </c>
+      <c r="B167" s="30" t="n">
+        <v>9090</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Peer — Misr Beni Suef profit</t>
-        </is>
-      </c>
-      <c r="B168" s="29" t="n">
-        <v>3946</v>
+          <t>Peer — Sinai Cement profit</t>
+        </is>
+      </c>
+      <c r="B168" s="30" t="n">
+        <v>2290</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
+          <t>Peer — Sinai Cement market capitalisation</t>
+        </is>
+      </c>
+      <c r="B169" s="30" t="n">
+        <v>20604.19</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Peer — Misr Beni Suef revenue</t>
+        </is>
+      </c>
+      <c r="B170" s="30" t="n">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Peer — Misr Beni Suef profit</t>
+        </is>
+      </c>
+      <c r="B171" s="30" t="n">
+        <v>3946</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
           <t>Peer — Misr Beni Suef market capitalisation</t>
         </is>
       </c>
-      <c r="B169" s="29" t="n">
+      <c r="B172" s="30" t="n">
         <v>13730</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="5" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
         <is>
           <t>Every cell on this sheet is BLUE — an input. Nothing here is computed from anything else here.</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="5" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
         <is>
           <t>Everything on every other sheet that can be derived from these is a formula.</t>
         </is>
@@ -7346,8 +7447,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A172:J172"/>
-    <mergeCell ref="A171:J171"/>
+    <mergeCell ref="A175:J175"/>
+    <mergeCell ref="A174:J174"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7431,7 +7532,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="32">
         <f>DCF!B33</f>
         <v/>
       </c>
@@ -7476,7 +7577,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="32">
         <f>DCF!B42</f>
         <v/>
       </c>
@@ -7536,7 +7637,7 @@
         </is>
       </c>
       <c r="C16" s="19">
-        <f>B7/Assumptions!$B$13/Assumptions!$B$11</f>
+        <f>B7/Assumptions!$B$14/Assumptions!$B$12</f>
         <v/>
       </c>
     </row>
@@ -7637,8 +7738,8 @@
           <t>Kiln clinker capacity (Mt, audited note 1)</t>
         </is>
       </c>
-      <c r="B5" s="32">
-        <f>Assumptions!$B$14</f>
+      <c r="B5" s="33">
+        <f>Assumptions!$B$15</f>
         <v/>
       </c>
     </row>
@@ -7649,7 +7750,7 @@
         </is>
       </c>
       <c r="B6" s="22">
-        <f>Assumptions!$B$22</f>
+        <f>Assumptions!$B$23</f>
         <v/>
       </c>
     </row>
@@ -7659,7 +7760,7 @@
           <t>Clinker produced (Mt)</t>
         </is>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="34">
         <f>B5*B6</f>
         <v/>
       </c>
@@ -7671,7 +7772,7 @@
         </is>
       </c>
       <c r="B8" s="22">
-        <f>Assumptions!$B$23</f>
+        <f>Assumptions!$B$24</f>
         <v/>
       </c>
     </row>
@@ -7681,7 +7782,7 @@
           <t>Clinker EXPORTED (Mt)</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="34">
         <f>B7*B8</f>
         <v/>
       </c>
@@ -7692,7 +7793,7 @@
           <t>Clinker ground into cement (Mt)</t>
         </is>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="34">
         <f>B7-B9</f>
         <v/>
       </c>
@@ -7703,8 +7804,8 @@
           <t>Clinker factor (t clinker / t cement)</t>
         </is>
       </c>
-      <c r="B11" s="34">
-        <f>Assumptions!$B$15</f>
+      <c r="B11" s="35">
+        <f>Assumptions!$B$16</f>
         <v/>
       </c>
     </row>
@@ -7714,7 +7815,7 @@
           <t>Cement produced (Mt)</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="36">
         <f>B10/B11</f>
         <v/>
       </c>
@@ -7725,8 +7826,8 @@
           <t>Cement mill capacity (Mt, audited note 1)</t>
         </is>
       </c>
-      <c r="B13" s="32">
-        <f>Assumptions!$B$13</f>
+      <c r="B13" s="33">
+        <f>Assumptions!$B$14</f>
         <v/>
       </c>
     </row>
@@ -7748,7 +7849,7 @@
         </is>
       </c>
       <c r="B15" s="22">
-        <f>Assumptions!$B$24</f>
+        <f>Assumptions!$B$25</f>
         <v/>
       </c>
     </row>
@@ -7758,7 +7859,7 @@
           <t>Cement EXPORTED (Mt)</t>
         </is>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="34">
         <f>B29*B15</f>
         <v/>
       </c>
@@ -7769,7 +7870,7 @@
           <t>Cement sold LOCALLY (Mt)</t>
         </is>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="34">
         <f>B29-B16</f>
         <v/>
       </c>
@@ -7780,7 +7881,7 @@
           <t>TOTAL DESPATCHES FY2025 (Mt)</t>
         </is>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="36">
         <f>B29+B9</f>
         <v/>
       </c>
@@ -7791,8 +7892,8 @@
           <t>Plus draw from finished-goods stock (Mt)</t>
         </is>
       </c>
-      <c r="B19" s="34">
-        <f>Assumptions!$B$25</f>
+      <c r="B19" s="35">
+        <f>Assumptions!$B$26</f>
         <v/>
       </c>
     </row>
@@ -7819,7 +7920,7 @@
         </is>
       </c>
       <c r="B21" s="14">
-        <f>Assumptions!$B$91</f>
+        <f>Assumptions!$B$92</f>
         <v/>
       </c>
     </row>
@@ -7829,7 +7930,7 @@
           <t>LOCAL CEMENT PRICE (EGP/t) — DERIVED</t>
         </is>
       </c>
-      <c r="B22" s="36">
+      <c r="B22" s="37">
         <f>B21/B17</f>
         <v/>
       </c>
@@ -7841,7 +7942,7 @@
         </is>
       </c>
       <c r="B23" s="14">
-        <f>Assumptions!$B$93</f>
+        <f>Assumptions!$B$94</f>
         <v/>
       </c>
     </row>
@@ -7851,8 +7952,8 @@
           <t>Clinker price as a fraction of cement</t>
         </is>
       </c>
-      <c r="B24" s="33">
-        <f>Assumptions!$B$17</f>
+      <c r="B24" s="34">
+        <f>Assumptions!$B$18</f>
         <v/>
       </c>
     </row>
@@ -7862,7 +7963,7 @@
           <t>Export cement-equivalent tonnes</t>
         </is>
       </c>
-      <c r="B25" s="33">
+      <c r="B25" s="34">
         <f>B16+B9*B24</f>
         <v/>
       </c>
@@ -7873,8 +7974,8 @@
           <t>EXPORT CEMENT PRICE (USD/t) — DERIVED</t>
         </is>
       </c>
-      <c r="B26" s="37">
-        <f>B23/B25/Assumptions!$B$18</f>
+      <c r="B26" s="38">
+        <f>B23/B25/Assumptions!$B$19</f>
         <v/>
       </c>
     </row>
@@ -7884,7 +7985,7 @@
           <t>EXPORT CLINKER PRICE (USD/t) — DERIVED</t>
         </is>
       </c>
-      <c r="B27" s="37">
+      <c r="B27" s="38">
         <f>B26*B24</f>
         <v/>
       </c>
@@ -7906,7 +8007,7 @@
           <t>Cement SOLD (Mt)</t>
         </is>
       </c>
-      <c r="B29" s="33">
+      <c r="B29" s="34">
         <f>B12+B19</f>
         <v/>
       </c>
@@ -7934,7 +8035,7 @@
         </is>
       </c>
       <c r="B31" s="14">
-        <f>Assumptions!$B$97</f>
+        <f>Assumptions!$B$98</f>
         <v/>
       </c>
     </row>
@@ -7945,7 +8046,7 @@
         </is>
       </c>
       <c r="B32" s="14">
-        <f>Assumptions!$B$98</f>
+        <f>Assumptions!$B$99</f>
         <v/>
       </c>
     </row>
@@ -7956,7 +8057,7 @@
         </is>
       </c>
       <c r="B33" s="17">
-        <f>Assumptions!$B$99+Assumptions!$B$61-Assumptions!$B$100</f>
+        <f>Assumptions!$B$100+Assumptions!$B$62-Assumptions!$B$101</f>
         <v/>
       </c>
     </row>
@@ -8010,7 +8111,7 @@
           <t>TOTAL CASH COST PER TONNE SOLD</t>
         </is>
       </c>
-      <c r="B38" s="36">
+      <c r="B38" s="37">
         <f>B34/B18</f>
         <v/>
       </c>
@@ -8085,27 +8186,27 @@
         </is>
       </c>
       <c r="B45" s="22">
-        <f>Assumptions!$B$22</f>
+        <f>Assumptions!$B$23</f>
         <v/>
       </c>
       <c r="C45" s="22">
-        <f>Assumptions!$C$22</f>
+        <f>Assumptions!$C$23</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>Assumptions!$D$22</f>
+        <f>Assumptions!$D$23</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>Assumptions!$E$22</f>
+        <f>Assumptions!$E$23</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>Assumptions!$F$22</f>
+        <f>Assumptions!$F$23</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>Assumptions!$G$22</f>
+        <f>Assumptions!$G$23</f>
         <v/>
       </c>
     </row>
@@ -8115,27 +8216,27 @@
           <t>Clinker produced (Mt)</t>
         </is>
       </c>
-      <c r="B46" s="33">
+      <c r="B46" s="34">
         <f>$B$5*B45</f>
         <v/>
       </c>
-      <c r="C46" s="33">
+      <c r="C46" s="34">
         <f>$B$5*C45</f>
         <v/>
       </c>
-      <c r="D46" s="33">
+      <c r="D46" s="34">
         <f>$B$5*D45</f>
         <v/>
       </c>
-      <c r="E46" s="33">
+      <c r="E46" s="34">
         <f>$B$5*E45</f>
         <v/>
       </c>
-      <c r="F46" s="33">
+      <c r="F46" s="34">
         <f>$B$5*F45</f>
         <v/>
       </c>
-      <c r="G46" s="33">
+      <c r="G46" s="34">
         <f>$B$5*G45</f>
         <v/>
       </c>
@@ -8147,27 +8248,27 @@
         </is>
       </c>
       <c r="B47" s="22">
-        <f>Assumptions!$B$23</f>
+        <f>Assumptions!$B$24</f>
         <v/>
       </c>
       <c r="C47" s="22">
-        <f>Assumptions!$C$23</f>
+        <f>Assumptions!$C$24</f>
         <v/>
       </c>
       <c r="D47" s="22">
-        <f>Assumptions!$D$23</f>
+        <f>Assumptions!$D$24</f>
         <v/>
       </c>
       <c r="E47" s="22">
-        <f>Assumptions!$E$23</f>
+        <f>Assumptions!$E$24</f>
         <v/>
       </c>
       <c r="F47" s="22">
-        <f>Assumptions!$F$23</f>
+        <f>Assumptions!$F$24</f>
         <v/>
       </c>
       <c r="G47" s="22">
-        <f>Assumptions!$G$23</f>
+        <f>Assumptions!$G$24</f>
         <v/>
       </c>
     </row>
@@ -8177,27 +8278,27 @@
           <t>Clinker exported (Mt)</t>
         </is>
       </c>
-      <c r="B48" s="33">
+      <c r="B48" s="34">
         <f>B46*B47</f>
         <v/>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="34">
         <f>C46*C47</f>
         <v/>
       </c>
-      <c r="D48" s="33">
+      <c r="D48" s="34">
         <f>D46*D47</f>
         <v/>
       </c>
-      <c r="E48" s="33">
+      <c r="E48" s="34">
         <f>E46*E47</f>
         <v/>
       </c>
-      <c r="F48" s="33">
+      <c r="F48" s="34">
         <f>F46*F47</f>
         <v/>
       </c>
-      <c r="G48" s="33">
+      <c r="G48" s="34">
         <f>G46*G47</f>
         <v/>
       </c>
@@ -8208,27 +8309,27 @@
           <t>Clinker ground (Mt)</t>
         </is>
       </c>
-      <c r="B49" s="33">
+      <c r="B49" s="34">
         <f>B46-B48</f>
         <v/>
       </c>
-      <c r="C49" s="33">
+      <c r="C49" s="34">
         <f>C46-C48</f>
         <v/>
       </c>
-      <c r="D49" s="33">
+      <c r="D49" s="34">
         <f>D46-D48</f>
         <v/>
       </c>
-      <c r="E49" s="33">
+      <c r="E49" s="34">
         <f>E46-E48</f>
         <v/>
       </c>
-      <c r="F49" s="33">
+      <c r="F49" s="34">
         <f>F46-F48</f>
         <v/>
       </c>
-      <c r="G49" s="33">
+      <c r="G49" s="34">
         <f>G46-G48</f>
         <v/>
       </c>
@@ -8239,27 +8340,27 @@
           <t>Cement produced (Mt)</t>
         </is>
       </c>
-      <c r="B50" s="33">
+      <c r="B50" s="34">
         <f>B49/$B$11</f>
         <v/>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="34">
         <f>C49/$B$11</f>
         <v/>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="34">
         <f>D49/$B$11</f>
         <v/>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="34">
         <f>E49/$B$11</f>
         <v/>
       </c>
-      <c r="F50" s="33">
+      <c r="F50" s="34">
         <f>F49/$B$11</f>
         <v/>
       </c>
-      <c r="G50" s="33">
+      <c r="G50" s="34">
         <f>G49/$B$11</f>
         <v/>
       </c>
@@ -8302,27 +8403,27 @@
         </is>
       </c>
       <c r="B52" s="22">
-        <f>Assumptions!$B$24</f>
+        <f>Assumptions!$B$25</f>
         <v/>
       </c>
       <c r="C52" s="22">
-        <f>Assumptions!$C$24</f>
+        <f>Assumptions!$C$25</f>
         <v/>
       </c>
       <c r="D52" s="22">
-        <f>Assumptions!$D$24</f>
+        <f>Assumptions!$D$25</f>
         <v/>
       </c>
       <c r="E52" s="22">
-        <f>Assumptions!$E$24</f>
+        <f>Assumptions!$E$25</f>
         <v/>
       </c>
       <c r="F52" s="22">
-        <f>Assumptions!$F$24</f>
+        <f>Assumptions!$F$25</f>
         <v/>
       </c>
       <c r="G52" s="22">
-        <f>Assumptions!$G$24</f>
+        <f>Assumptions!$G$25</f>
         <v/>
       </c>
     </row>
@@ -8332,27 +8433,27 @@
           <t>Cement exported (Mt)</t>
         </is>
       </c>
-      <c r="B53" s="33">
+      <c r="B53" s="34">
         <f>B75*B52</f>
         <v/>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="34">
         <f>C75*C52</f>
         <v/>
       </c>
-      <c r="D53" s="33">
+      <c r="D53" s="34">
         <f>D75*D52</f>
         <v/>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="34">
         <f>E75*E52</f>
         <v/>
       </c>
-      <c r="F53" s="33">
+      <c r="F53" s="34">
         <f>F75*F52</f>
         <v/>
       </c>
-      <c r="G53" s="33">
+      <c r="G53" s="34">
         <f>G75*G52</f>
         <v/>
       </c>
@@ -8363,27 +8464,27 @@
           <t>Cement local (Mt)</t>
         </is>
       </c>
-      <c r="B54" s="33">
+      <c r="B54" s="34">
         <f>B75-B53</f>
         <v/>
       </c>
-      <c r="C54" s="33">
+      <c r="C54" s="34">
         <f>C75-C53</f>
         <v/>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="34">
         <f>D75-D53</f>
         <v/>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="34">
         <f>E75-E53</f>
         <v/>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="34">
         <f>F75-F53</f>
         <v/>
       </c>
-      <c r="G54" s="33">
+      <c r="G54" s="34">
         <f>G75-G53</f>
         <v/>
       </c>
@@ -8394,27 +8495,27 @@
           <t>TOTAL DESPATCHES (Mt)</t>
         </is>
       </c>
-      <c r="B55" s="35">
+      <c r="B55" s="36">
         <f>B75+B48</f>
         <v/>
       </c>
-      <c r="C55" s="35">
+      <c r="C55" s="36">
         <f>C75+C48</f>
         <v/>
       </c>
-      <c r="D55" s="35">
+      <c r="D55" s="36">
         <f>D75+D48</f>
         <v/>
       </c>
-      <c r="E55" s="35">
+      <c r="E55" s="36">
         <f>E75+E48</f>
         <v/>
       </c>
-      <c r="F55" s="35">
+      <c r="F55" s="36">
         <f>F75+F48</f>
         <v/>
       </c>
-      <c r="G55" s="35">
+      <c r="G55" s="36">
         <f>G75+G48</f>
         <v/>
       </c>
@@ -8426,27 +8527,27 @@
         </is>
       </c>
       <c r="B56" s="17">
-        <f>$B$22*Assumptions!$B$26</f>
+        <f>$B$22*Assumptions!$B$27</f>
         <v/>
       </c>
       <c r="C56" s="17">
-        <f>$B$22*Assumptions!$C$26*Assumptions!$B$142</f>
+        <f>$B$22*Assumptions!$C$27*Assumptions!$B$143</f>
         <v/>
       </c>
       <c r="D56" s="17">
-        <f>$B$22*Assumptions!$D$26*Assumptions!$B$142</f>
+        <f>$B$22*Assumptions!$D$27*Assumptions!$B$143</f>
         <v/>
       </c>
       <c r="E56" s="17">
-        <f>$B$22*Assumptions!$E$26*Assumptions!$B$142</f>
+        <f>$B$22*Assumptions!$E$27*Assumptions!$B$143</f>
         <v/>
       </c>
       <c r="F56" s="17">
-        <f>$B$22*Assumptions!$F$26*Assumptions!$B$142</f>
+        <f>$B$22*Assumptions!$F$27*Assumptions!$B$143</f>
         <v/>
       </c>
       <c r="G56" s="17">
-        <f>$B$22*Assumptions!$G$26*Assumptions!$B$142</f>
+        <f>$B$22*Assumptions!$G$27*Assumptions!$B$143</f>
         <v/>
       </c>
     </row>
@@ -8457,27 +8558,27 @@
         </is>
       </c>
       <c r="B57" s="17">
-        <f>$B$26*Assumptions!$B$27*Assumptions!$B$28</f>
+        <f>$B$26*Assumptions!$B$28*Assumptions!$B$29</f>
         <v/>
       </c>
       <c r="C57" s="17">
-        <f>$B$26*Assumptions!$C$27*Assumptions!$C$28*Assumptions!$B$143</f>
+        <f>$B$26*Assumptions!$C$28*Assumptions!$C$29*Assumptions!$B$144</f>
         <v/>
       </c>
       <c r="D57" s="17">
-        <f>$B$26*Assumptions!$D$27*Assumptions!$D$28*Assumptions!$B$143</f>
+        <f>$B$26*Assumptions!$D$28*Assumptions!$D$29*Assumptions!$B$144</f>
         <v/>
       </c>
       <c r="E57" s="17">
-        <f>$B$26*Assumptions!$E$27*Assumptions!$E$28*Assumptions!$B$143</f>
+        <f>$B$26*Assumptions!$E$28*Assumptions!$E$29*Assumptions!$B$144</f>
         <v/>
       </c>
       <c r="F57" s="17">
-        <f>$B$26*Assumptions!$F$27*Assumptions!$F$28*Assumptions!$B$143</f>
+        <f>$B$26*Assumptions!$F$28*Assumptions!$F$29*Assumptions!$B$144</f>
         <v/>
       </c>
       <c r="G57" s="17">
-        <f>$B$26*Assumptions!$G$27*Assumptions!$G$28*Assumptions!$B$143</f>
+        <f>$B$26*Assumptions!$G$28*Assumptions!$G$29*Assumptions!$B$144</f>
         <v/>
       </c>
     </row>
@@ -8642,28 +8743,28 @@
           <t>REVENUE (EGP mn)</t>
         </is>
       </c>
-      <c r="B63" s="36">
-        <f>B62*(1+Assumptions!$B$19)</f>
-        <v/>
-      </c>
-      <c r="C63" s="36">
-        <f>C62*(1+Assumptions!$B$145)</f>
-        <v/>
-      </c>
-      <c r="D63" s="36">
-        <f>D62*(1+Assumptions!$B$145)</f>
-        <v/>
-      </c>
-      <c r="E63" s="36">
-        <f>E62*(1+Assumptions!$B$145)</f>
-        <v/>
-      </c>
-      <c r="F63" s="36">
-        <f>F62*(1+Assumptions!$B$145)</f>
-        <v/>
-      </c>
-      <c r="G63" s="36">
-        <f>G62*(1+Assumptions!$B$145)</f>
+      <c r="B63" s="37">
+        <f>B62*(1+Assumptions!$B$20)</f>
+        <v/>
+      </c>
+      <c r="C63" s="37">
+        <f>C62*(1+Assumptions!$B$146)</f>
+        <v/>
+      </c>
+      <c r="D63" s="37">
+        <f>D62*(1+Assumptions!$B$146)</f>
+        <v/>
+      </c>
+      <c r="E63" s="37">
+        <f>E62*(1+Assumptions!$B$146)</f>
+        <v/>
+      </c>
+      <c r="F63" s="37">
+        <f>F62*(1+Assumptions!$B$146)</f>
+        <v/>
+      </c>
+      <c r="G63" s="37">
+        <f>G62*(1+Assumptions!$B$146)</f>
         <v/>
       </c>
     </row>
@@ -8705,27 +8806,27 @@
         </is>
       </c>
       <c r="B65" s="17">
-        <f>$B$35*Assumptions!$B$29*(1-Assumptions!$B$30)*B46</f>
+        <f>$B$35*Assumptions!$B$30*(1-Assumptions!$B$31)*B46</f>
         <v/>
       </c>
       <c r="C65" s="17">
-        <f>$B$35*Assumptions!$C$29*(1-Assumptions!$C$30)*C46*Assumptions!$B$144</f>
+        <f>$B$35*Assumptions!$C$30*(1-Assumptions!$C$31)*C46*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="D65" s="17">
-        <f>$B$35*Assumptions!$D$29*(1-Assumptions!$D$30)*D46*Assumptions!$B$144</f>
+        <f>$B$35*Assumptions!$D$30*(1-Assumptions!$D$31)*D46*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="E65" s="17">
-        <f>$B$35*Assumptions!$E$29*(1-Assumptions!$E$30)*E46*Assumptions!$B$144</f>
+        <f>$B$35*Assumptions!$E$30*(1-Assumptions!$E$31)*E46*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="F65" s="17">
-        <f>$B$35*Assumptions!$F$29*(1-Assumptions!$F$30)*F46*Assumptions!$B$144</f>
+        <f>$B$35*Assumptions!$F$30*(1-Assumptions!$F$31)*F46*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="G65" s="17">
-        <f>$B$35*Assumptions!$G$29*(1-Assumptions!$G$30)*G46*Assumptions!$B$144</f>
+        <f>$B$35*Assumptions!$G$30*(1-Assumptions!$G$31)*G46*Assumptions!$B$145</f>
         <v/>
       </c>
     </row>
@@ -8736,27 +8837,27 @@
         </is>
       </c>
       <c r="B66" s="17">
-        <f>$B$36*Assumptions!$B$29*B55</f>
+        <f>$B$36*Assumptions!$B$30*B55</f>
         <v/>
       </c>
       <c r="C66" s="17">
-        <f>$B$36*Assumptions!$C$29*C55*Assumptions!$B$144</f>
+        <f>$B$36*Assumptions!$C$30*C55*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="D66" s="17">
-        <f>$B$36*Assumptions!$D$29*D55*Assumptions!$B$144</f>
+        <f>$B$36*Assumptions!$D$30*D55*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="E66" s="17">
-        <f>$B$36*Assumptions!$E$29*E55*Assumptions!$B$144</f>
+        <f>$B$36*Assumptions!$E$30*E55*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="F66" s="17">
-        <f>$B$36*Assumptions!$F$29*F55*Assumptions!$B$144</f>
+        <f>$B$36*Assumptions!$F$30*F55*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="G66" s="17">
-        <f>$B$36*Assumptions!$G$29*G55*Assumptions!$B$144</f>
+        <f>$B$36*Assumptions!$G$30*G55*Assumptions!$B$145</f>
         <v/>
       </c>
     </row>
@@ -8767,27 +8868,27 @@
         </is>
       </c>
       <c r="B67" s="17">
-        <f>$B$37*Assumptions!$B$29*B55</f>
+        <f>$B$37*Assumptions!$B$30*B55</f>
         <v/>
       </c>
       <c r="C67" s="17">
-        <f>$B$37*Assumptions!$C$29*C55*Assumptions!$B$144</f>
+        <f>$B$37*Assumptions!$C$30*C55*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="D67" s="17">
-        <f>$B$37*Assumptions!$D$29*D55*Assumptions!$B$144</f>
+        <f>$B$37*Assumptions!$D$30*D55*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="E67" s="17">
-        <f>$B$37*Assumptions!$E$29*E55*Assumptions!$B$144</f>
+        <f>$B$37*Assumptions!$E$30*E55*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="F67" s="17">
-        <f>$B$37*Assumptions!$F$29*F55*Assumptions!$B$144</f>
+        <f>$B$37*Assumptions!$F$30*F55*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="G67" s="17">
-        <f>$B$37*Assumptions!$G$29*G55*Assumptions!$B$144</f>
+        <f>$B$37*Assumptions!$G$30*G55*Assumptions!$B$145</f>
         <v/>
       </c>
     </row>
@@ -8860,27 +8961,27 @@
         </is>
       </c>
       <c r="B70" s="17">
-        <f>(Assumptions!$B$64+Assumptions!$B$67)/Assumptions!$B$55*B63</f>
+        <f>(Assumptions!$B$65+Assumptions!$B$68)/Assumptions!$B$56*B63</f>
         <v/>
       </c>
       <c r="C70" s="17">
-        <f>(Assumptions!$B$64+Assumptions!$B$67)/Assumptions!$B$55*C63</f>
+        <f>(Assumptions!$B$65+Assumptions!$B$68)/Assumptions!$B$56*C63</f>
         <v/>
       </c>
       <c r="D70" s="17">
-        <f>(Assumptions!$B$64+Assumptions!$B$67)/Assumptions!$B$55*D63</f>
+        <f>(Assumptions!$B$65+Assumptions!$B$68)/Assumptions!$B$56*D63</f>
         <v/>
       </c>
       <c r="E70" s="17">
-        <f>(Assumptions!$B$64+Assumptions!$B$67)/Assumptions!$B$55*E63</f>
+        <f>(Assumptions!$B$65+Assumptions!$B$68)/Assumptions!$B$56*E63</f>
         <v/>
       </c>
       <c r="F70" s="17">
-        <f>(Assumptions!$B$64+Assumptions!$B$67)/Assumptions!$B$55*F63</f>
+        <f>(Assumptions!$B$65+Assumptions!$B$68)/Assumptions!$B$56*F63</f>
         <v/>
       </c>
       <c r="G70" s="17">
-        <f>(Assumptions!$B$64+Assumptions!$B$67)/Assumptions!$B$55*G63</f>
+        <f>(Assumptions!$B$65+Assumptions!$B$68)/Assumptions!$B$56*G63</f>
         <v/>
       </c>
     </row>
@@ -8890,27 +8991,27 @@
           <t>EBITDA  (AN OUTPUT)</t>
         </is>
       </c>
-      <c r="B71" s="36">
+      <c r="B71" s="37">
         <f>B63-B68-B70</f>
         <v/>
       </c>
-      <c r="C71" s="36">
+      <c r="C71" s="37">
         <f>C63-C68-C70</f>
         <v/>
       </c>
-      <c r="D71" s="36">
+      <c r="D71" s="37">
         <f>D63-D68-D70</f>
         <v/>
       </c>
-      <c r="E71" s="36">
+      <c r="E71" s="37">
         <f>E63-E68-E70</f>
         <v/>
       </c>
-      <c r="F71" s="36">
+      <c r="F71" s="37">
         <f>F63-F68-F70</f>
         <v/>
       </c>
-      <c r="G71" s="36">
+      <c r="G71" s="37">
         <f>G63-G68-G70</f>
         <v/>
       </c>
@@ -8983,28 +9084,28 @@
           <t>Draw from finished-goods stock (Mt)  (DRIVER)</t>
         </is>
       </c>
-      <c r="B74" s="34">
-        <f>Assumptions!$B$25</f>
-        <v/>
-      </c>
-      <c r="C74" s="34">
-        <f>Assumptions!$C$25</f>
-        <v/>
-      </c>
-      <c r="D74" s="34">
-        <f>Assumptions!$D$25</f>
-        <v/>
-      </c>
-      <c r="E74" s="34">
-        <f>Assumptions!$E$25</f>
-        <v/>
-      </c>
-      <c r="F74" s="34">
-        <f>Assumptions!$F$25</f>
-        <v/>
-      </c>
-      <c r="G74" s="34">
-        <f>Assumptions!$G$25</f>
+      <c r="B74" s="35">
+        <f>Assumptions!$B$26</f>
+        <v/>
+      </c>
+      <c r="C74" s="35">
+        <f>Assumptions!$C$26</f>
+        <v/>
+      </c>
+      <c r="D74" s="35">
+        <f>Assumptions!$D$26</f>
+        <v/>
+      </c>
+      <c r="E74" s="35">
+        <f>Assumptions!$E$26</f>
+        <v/>
+      </c>
+      <c r="F74" s="35">
+        <f>Assumptions!$F$26</f>
+        <v/>
+      </c>
+      <c r="G74" s="35">
+        <f>Assumptions!$G$26</f>
         <v/>
       </c>
     </row>
@@ -9014,27 +9115,27 @@
           <t>VALIDATION — AND A PRICE TEST THAT CAN ACTUALLY FAIL</t>
         </is>
       </c>
-      <c r="B75" s="38">
+      <c r="B75" s="39">
         <f>B50+B74</f>
         <v/>
       </c>
-      <c r="C75" s="38">
+      <c r="C75" s="39">
         <f>C50+C74</f>
         <v/>
       </c>
-      <c r="D75" s="38">
+      <c r="D75" s="39">
         <f>D50+D74</f>
         <v/>
       </c>
-      <c r="E75" s="38">
+      <c r="E75" s="39">
         <f>E50+E74</f>
         <v/>
       </c>
-      <c r="F75" s="38">
+      <c r="F75" s="39">
         <f>F50+F74</f>
         <v/>
       </c>
-      <c r="G75" s="38">
+      <c r="G75" s="39">
         <f>G50+G74</f>
         <v/>
       </c>
@@ -9060,7 +9161,7 @@
         </is>
       </c>
       <c r="B77" s="14">
-        <f>Assumptions!$B$55</f>
+        <f>Assumptions!$B$56</f>
         <v/>
       </c>
     </row>
@@ -9179,8 +9280,8 @@
           <t>Kiln clinker capacity (Mt, audited note 1)</t>
         </is>
       </c>
-      <c r="B92" s="32">
-        <f>Assumptions!$B$14</f>
+      <c r="B92" s="33">
+        <f>Assumptions!$B$15</f>
         <v/>
       </c>
     </row>
@@ -9190,7 +9291,7 @@
           <t>Peak clinker required across the forecast (Mt)</t>
         </is>
       </c>
-      <c r="B93" s="33">
+      <c r="B93" s="34">
         <f>MAX(C46:G46)</f>
         <v/>
       </c>
@@ -9212,7 +9313,7 @@
           <t>Headroom at the kiln (Mt of clinker)</t>
         </is>
       </c>
-      <c r="B95" s="33">
+      <c r="B95" s="34">
         <f>B92-B93</f>
         <v/>
       </c>
@@ -9223,8 +9324,8 @@
           <t>Cement mill capacity (Mt, audited note 1)</t>
         </is>
       </c>
-      <c r="B96" s="32">
-        <f>Assumptions!$B$13</f>
+      <c r="B96" s="33">
+        <f>Assumptions!$B$14</f>
         <v/>
       </c>
     </row>
@@ -9234,7 +9335,7 @@
           <t>Peak cement produced across the forecast (Mt)</t>
         </is>
       </c>
-      <c r="B97" s="33">
+      <c r="B97" s="34">
         <f>MAX(C50:G50)</f>
         <v/>
       </c>
@@ -9256,7 +9357,7 @@
           <t>Headroom at the mill (Mt of cement)</t>
         </is>
       </c>
-      <c r="B99" s="33">
+      <c r="B99" s="34">
         <f>B96-B97</f>
         <v/>
       </c>
@@ -9368,7 +9469,7 @@
         </is>
       </c>
       <c r="B5" s="17">
-        <f>Assumptions!$B$55</f>
+        <f>Assumptions!$B$56</f>
         <v/>
       </c>
     </row>
@@ -9379,7 +9480,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>Assumptions!$B$157</f>
+        <f>Assumptions!$B$158</f>
         <v/>
       </c>
     </row>
@@ -9401,7 +9502,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>Assumptions!$B$156</f>
+        <f>Assumptions!$B$157</f>
         <v/>
       </c>
     </row>
@@ -9411,7 +9512,7 @@
           <t>Normalised EBITDA</t>
         </is>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="37">
         <f>B7*B8</f>
         <v/>
       </c>
@@ -9423,7 +9524,7 @@
         </is>
       </c>
       <c r="B10" s="17">
-        <f>-Assumptions!$B$82</f>
+        <f>-Assumptions!$B$83</f>
         <v/>
       </c>
     </row>
@@ -9444,7 +9545,7 @@
           <t>Normalised NOPAT</t>
         </is>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="37">
         <f>B11*(1-Assumptions!$B$9)</f>
         <v/>
       </c>
@@ -9501,8 +9602,8 @@
           <t>Justified EV/EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="39">
-        <f>Assumptions!$B$154</f>
+      <c r="B18" s="40">
+        <f>Assumptions!$B$155</f>
         <v/>
       </c>
     </row>
@@ -9580,8 +9681,8 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="B26" s="39">
-        <f>Assumptions!$B$155</f>
+      <c r="B26" s="40">
+        <f>Assumptions!$B$156</f>
         <v/>
       </c>
     </row>
@@ -9811,23 +9912,23 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>B5*Assumptions!$B$33*Assumptions!$B$146</f>
+        <f>B5*Assumptions!$B$34*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>C5*Assumptions!$C$33*Assumptions!$B$146</f>
+        <f>C5*Assumptions!$C$34*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>D5*Assumptions!$D$33*Assumptions!$B$146</f>
+        <f>D5*Assumptions!$D$34*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>E5*Assumptions!$E$33*Assumptions!$B$146</f>
+        <f>E5*Assumptions!$E$34*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>F5*Assumptions!$F$33*Assumptions!$B$146</f>
+        <f>F5*Assumptions!$F$34*Assumptions!$B$147</f>
         <v/>
       </c>
     </row>
@@ -9838,23 +9939,23 @@
         </is>
       </c>
       <c r="B9" s="17">
-        <f>B7-B8+Assumptions!$B$147*'Segments'!C60+Assumptions!$B$147*'Segments'!C61+Assumptions!$B$148*Assumptions!$C$29</f>
+        <f>B7-B8+Assumptions!$B$148*'Segments'!C60+Assumptions!$B$148*'Segments'!C61+Assumptions!$B$149*Assumptions!$C$30</f>
         <v/>
       </c>
       <c r="C9" s="17">
-        <f>C7-C8+Assumptions!$B$147*'Segments'!D60+Assumptions!$B$147*'Segments'!D61+Assumptions!$B$148*Assumptions!$D$29</f>
+        <f>C7-C8+Assumptions!$B$148*'Segments'!D60+Assumptions!$B$148*'Segments'!D61+Assumptions!$B$149*Assumptions!$D$30</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>D7-D8+Assumptions!$B$147*'Segments'!E60+Assumptions!$B$147*'Segments'!E61+Assumptions!$B$148*Assumptions!$E$29</f>
+        <f>D7-D8+Assumptions!$B$148*'Segments'!E60+Assumptions!$B$148*'Segments'!E61+Assumptions!$B$149*Assumptions!$E$30</f>
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>E7-E8+Assumptions!$B$147*'Segments'!F60+Assumptions!$B$147*'Segments'!F61+Assumptions!$B$148*Assumptions!$F$29</f>
+        <f>E7-E8+Assumptions!$B$148*'Segments'!F60+Assumptions!$B$148*'Segments'!F61+Assumptions!$B$149*Assumptions!$F$30</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>F7-F8+Assumptions!$B$147*'Segments'!G60+Assumptions!$B$147*'Segments'!G61+Assumptions!$B$148*Assumptions!$G$29</f>
+        <f>F7-F8+Assumptions!$B$148*'Segments'!G60+Assumptions!$B$148*'Segments'!G61+Assumptions!$B$149*Assumptions!$G$30</f>
         <v/>
       </c>
     </row>
@@ -9946,23 +10047,23 @@
         </is>
       </c>
       <c r="B13" s="17">
-        <f>-Assumptions!$B$13*Assumptions!$B$36*Assumptions!$C$28</f>
+        <f>-Assumptions!$B$14*Assumptions!$B$37*Assumptions!$C$29</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>-Assumptions!$B$13*Assumptions!$B$36*Assumptions!$D$28</f>
+        <f>-Assumptions!$B$14*Assumptions!$B$37*Assumptions!$D$29</f>
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>-Assumptions!$B$13*Assumptions!$B$36*Assumptions!$E$28</f>
+        <f>-Assumptions!$B$14*Assumptions!$B$37*Assumptions!$E$29</f>
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>-Assumptions!$B$13*Assumptions!$B$36*Assumptions!$F$28</f>
+        <f>-Assumptions!$B$14*Assumptions!$B$37*Assumptions!$F$29</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>-Assumptions!$B$13*Assumptions!$B$36*Assumptions!$G$28</f>
+        <f>-Assumptions!$B$14*Assumptions!$B$37*Assumptions!$G$29</f>
         <v/>
       </c>
     </row>
@@ -9973,23 +10074,23 @@
         </is>
       </c>
       <c r="B14" s="17">
-        <f>-(B5-Assumptions!$B$55)*Assumptions!$B$37</f>
+        <f>-(B5-Assumptions!$B$56)*Assumptions!$B$38</f>
         <v/>
       </c>
       <c r="C14" s="17">
-        <f>-(C5-B5)*Assumptions!$B$37</f>
+        <f>-(C5-B5)*Assumptions!$B$38</f>
         <v/>
       </c>
       <c r="D14" s="17">
-        <f>-(D5-C5)*Assumptions!$B$37</f>
+        <f>-(D5-C5)*Assumptions!$B$38</f>
         <v/>
       </c>
       <c r="E14" s="17">
-        <f>-(E5-D5)*Assumptions!$B$37</f>
+        <f>-(E5-D5)*Assumptions!$B$38</f>
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>-(F5-E5)*Assumptions!$B$37</f>
+        <f>-(F5-E5)*Assumptions!$B$38</f>
         <v/>
       </c>
     </row>
@@ -9999,23 +10100,23 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B15" s="36">
-        <f>(B11+B12+B13+B14)*(1-Assumptions!$B$51)</f>
-        <v/>
-      </c>
-      <c r="C15" s="36">
+      <c r="B15" s="37">
+        <f>(B11+B12+B13+B14)*(1-Assumptions!$B$52)</f>
+        <v/>
+      </c>
+      <c r="C15" s="37">
         <f>C11+C12+C13+C14</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="37">
         <f>D11+D12+D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="37">
         <f>E11+E12+E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="37">
         <f>F11+F12+F13+F14</f>
         <v/>
       </c>
@@ -10026,24 +10127,24 @@
           <t>Glide fraction</t>
         </is>
       </c>
-      <c r="B16" s="40">
-        <f>(Assumptions!$B$34-Assumptions!$B$34)/(Assumptions!$B$34-Assumptions!$F$34)</f>
-        <v/>
-      </c>
-      <c r="C16" s="40">
-        <f>(Assumptions!$B$34-Assumptions!$C$34)/(Assumptions!$B$34-Assumptions!$F$34)</f>
-        <v/>
-      </c>
-      <c r="D16" s="40">
-        <f>(Assumptions!$B$34-Assumptions!$D$34)/(Assumptions!$B$34-Assumptions!$F$34)</f>
-        <v/>
-      </c>
-      <c r="E16" s="40">
-        <f>(Assumptions!$B$34-Assumptions!$E$34)/(Assumptions!$B$34-Assumptions!$F$34)</f>
-        <v/>
-      </c>
-      <c r="F16" s="40">
-        <f>(Assumptions!$B$34-Assumptions!$F$34)/(Assumptions!$B$34-Assumptions!$F$34)</f>
+      <c r="B16" s="41">
+        <f>(Assumptions!$B$35-Assumptions!$B$35)/(Assumptions!$B$35-Assumptions!$F$35)</f>
+        <v/>
+      </c>
+      <c r="C16" s="41">
+        <f>(Assumptions!$B$35-Assumptions!$C$35)/(Assumptions!$B$35-Assumptions!$F$35)</f>
+        <v/>
+      </c>
+      <c r="D16" s="41">
+        <f>(Assumptions!$B$35-Assumptions!$D$35)/(Assumptions!$B$35-Assumptions!$F$35)</f>
+        <v/>
+      </c>
+      <c r="E16" s="41">
+        <f>(Assumptions!$B$35-Assumptions!$E$35)/(Assumptions!$B$35-Assumptions!$F$35)</f>
+        <v/>
+      </c>
+      <c r="F16" s="41">
+        <f>(Assumptions!$B$35-Assumptions!$F$35)/(Assumptions!$B$35-Assumptions!$F$35)</f>
         <v/>
       </c>
     </row>
@@ -10053,23 +10154,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B17" s="41">
+      <c r="B17" s="42">
         <f>$C$40-($C$40-$C$50)*B16</f>
         <v/>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="42">
         <f>$C$40-($C$40-$C$50)*C16</f>
         <v/>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="42">
         <f>$C$40-($C$40-$C$50)*D16</f>
         <v/>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="42">
         <f>$C$40-($C$40-$C$50)*E16</f>
         <v/>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="42">
         <f>$C$40-($C$40-$C$50)*F16</f>
         <v/>
       </c>
@@ -10080,24 +10181,24 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B18" s="40">
-        <f>1/(1+B17)^((1-Assumptions!$B$51)/2)</f>
-        <v/>
-      </c>
-      <c r="C18" s="40">
-        <f>1/((1+B17)^(1-Assumptions!$B$51)*(1+C17)^0.5)</f>
-        <v/>
-      </c>
-      <c r="D18" s="40">
-        <f>1/((1+B17)^(1-Assumptions!$B$51)*(1+C17)*(1+D17)^0.5)</f>
-        <v/>
-      </c>
-      <c r="E18" s="40">
-        <f>1/((1+B17)^(1-Assumptions!$B$51)*(1+C17)*(1+D17)*(1+E17)^0.5)</f>
-        <v/>
-      </c>
-      <c r="F18" s="40">
-        <f>1/((1+B17)^(1-Assumptions!$B$51)*(1+C17)*(1+D17)*(1+E17)*(1+F17)^0.5)</f>
+      <c r="B18" s="41">
+        <f>1/(1+B17)^((1-Assumptions!$B$52)/2)</f>
+        <v/>
+      </c>
+      <c r="C18" s="41">
+        <f>1/((1+B17)^(1-Assumptions!$B$52)*(1+C17)^0.5)</f>
+        <v/>
+      </c>
+      <c r="D18" s="41">
+        <f>1/((1+B17)^(1-Assumptions!$B$52)*(1+C17)*(1+D17)^0.5)</f>
+        <v/>
+      </c>
+      <c r="E18" s="41">
+        <f>1/((1+B17)^(1-Assumptions!$B$52)*(1+C17)*(1+D17)*(1+E17)^0.5)</f>
+        <v/>
+      </c>
+      <c r="F18" s="41">
+        <f>1/((1+B17)^(1-Assumptions!$B$52)*(1+C17)*(1+D17)*(1+E17)*(1+F17)^0.5)</f>
         <v/>
       </c>
     </row>
@@ -10149,7 +10250,7 @@
         </is>
       </c>
       <c r="B22" s="17">
-        <f>Assumptions!$B$13*Assumptions!$B$152*Assumptions!$B$11*Assumptions!$G$29</f>
+        <f>Assumptions!$B$14*Assumptions!$B$153*Assumptions!$B$12*Assumptions!$G$30</f>
         <v/>
       </c>
       <c r="C22" t="inlineStr">
@@ -10169,7 +10270,7 @@
         </is>
       </c>
       <c r="B23" s="17">
-        <f>F11*(1+Assumptions!$B$50)</f>
+        <f>F11*(1+Assumptions!$B$51)</f>
         <v/>
       </c>
       <c r="C23" t="inlineStr">
@@ -10185,7 +10286,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Memo: return on invested capital at replacement cost</t>
+          <t>Memo: return on invested capital — RETIRED construction (profit grown one year against a capital base that has not)</t>
         </is>
       </c>
       <c r="B24" s="8">
@@ -10198,7 +10299,7 @@
         </is>
       </c>
       <c r="D24" s="17">
-        <f>Assumptions!$B$50*F5*0.12000000</f>
+        <f>Assumptions!$B$51*F5*0.12000000</f>
         <v/>
       </c>
     </row>
@@ -10209,7 +10310,7 @@
         </is>
       </c>
       <c r="B25" s="8">
-        <f>('Income Statement'!D12*(1-Assumptions!$B$9))/(Assumptions!$B$115+$C$44)</f>
+        <f>('Income Statement'!D12*(1-Assumptions!$B$9))/(Assumptions!$B$116+$C$44)</f>
         <v/>
       </c>
       <c r="C25" t="inlineStr">
@@ -10218,7 +10319,7 @@
         </is>
       </c>
       <c r="D25" s="17">
-        <f>((1+Assumptions!$B$50)/(1+0.07000000)-1)*B22</f>
+        <f>((1+Assumptions!$B$51)/(1+0.07000000)-1)*B22</f>
         <v/>
       </c>
     </row>
@@ -10229,7 +10330,7 @@
         </is>
       </c>
       <c r="B26" s="8">
-        <f>Assumptions!$B$50/B24</f>
+        <f>Assumptions!$B$51/B24</f>
         <v/>
       </c>
       <c r="C26" t="inlineStr">
@@ -10249,7 +10350,16 @@
         </is>
       </c>
       <c r="B27" s="17">
-        <f>D26*(1+Assumptions!$B$50)/($C$50-Assumptions!$B$50)</f>
+        <f>D26*(1+Assumptions!$B$51)/($C$50-Assumptions!$B$51)</f>
+        <v/>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Memo: return on invested capital ADOPTED — profit and capital at the SAME date (B23 ungrown, over B22)</t>
+        </is>
+      </c>
+      <c r="D27" s="8">
+        <f>B23/(1+Assumptions!$B$51)/B22</f>
         <v/>
       </c>
     </row>
@@ -10267,11 +10377,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>End-of-window discount factor  (t = 4.417y, not the year-5 mid-point)</t>
-        </is>
-      </c>
-      <c r="B29" s="40">
-        <f>1/((1+B17)^(1-Assumptions!$B$51)*(1+C17)*(1+D17)*(1+E17)*(1+F17))</f>
+          <t>End-of-window discount factor  (t = 4.50y, not the year-5 mid-point)</t>
+        </is>
+      </c>
+      <c r="B29" s="41">
+        <f>1/((1+B17)^(1-Assumptions!$B$52)*(1+C17)*(1+D17)*(1+E17)*(1+F17))</f>
         <v/>
       </c>
     </row>
@@ -10317,7 +10427,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B33" s="36">
+      <c r="B33" s="37">
         <f>B31+B32</f>
         <v/>
       </c>
@@ -10340,7 +10450,7 @@
         </is>
       </c>
       <c r="B35" s="17">
-        <f>Assumptions!$B$139</f>
+        <f>Assumptions!$B$140</f>
         <v/>
       </c>
       <c r="E35" t="inlineStr">
@@ -10356,11 +10466,11 @@
         </is>
       </c>
       <c r="B36" s="17">
-        <f>Assumptions!$B$112+B15/(1-Assumptions!$B$51)*Assumptions!$B$51+Assumptions!$B$112*Assumptions!$B$35*Assumptions!$B$51*(1-Assumptions!$B$9)-Assumptions!$B$131</f>
-        <v/>
-      </c>
-      <c r="C36" s="41">
-        <f>Assumptions!$B$40</f>
+        <f>Assumptions!$B$113+B15/(1-Assumptions!$B$52)*Assumptions!$B$52+Assumptions!$B$113*Assumptions!$B$36*Assumptions!$B$52*(1-Assumptions!$B$9)-Assumptions!$B$132</f>
+        <v/>
+      </c>
+      <c r="C36" s="42">
+        <f>Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="E36" t="inlineStr">
@@ -10375,12 +10485,12 @@
           <t>(memo) what that roll-forward missed, per share</t>
         </is>
       </c>
-      <c r="B37" s="42">
-        <f>(B36-Assumptions!$B$138-B38-B39)/B43</f>
-        <v/>
-      </c>
-      <c r="C37" s="41">
-        <f>-Assumptions!$B$41</f>
+      <c r="B37" s="43">
+        <f>(B36-Assumptions!$B$139-B38-B39)/B43</f>
+        <v/>
+      </c>
+      <c r="C37" s="42">
+        <f>-Assumptions!$B$42</f>
         <v/>
       </c>
       <c r="E37" t="inlineStr">
@@ -10396,10 +10506,10 @@
         </is>
       </c>
       <c r="B38" s="17">
-        <f>Assumptions!$B$139</f>
-        <v/>
-      </c>
-      <c r="C38" s="41">
+        <f>Assumptions!$B$140</f>
+        <v/>
+      </c>
+      <c r="C38" s="42">
         <f>C36+C37</f>
         <v/>
       </c>
@@ -10416,11 +10526,11 @@
         </is>
       </c>
       <c r="B39" s="17">
-        <f>-Assumptions!$B$140</f>
-        <v/>
-      </c>
-      <c r="C39" s="41">
-        <f>C38+Assumptions!$B$10*Assumptions!$B$42</f>
+        <f>-Assumptions!$B$141</f>
+        <v/>
+      </c>
+      <c r="C39" s="42">
+        <f>C38+Assumptions!$B$10*Assumptions!$B$43</f>
         <v/>
       </c>
       <c r="E39" t="inlineStr">
@@ -10439,7 +10549,7 @@
         <f>B38+B39</f>
         <v/>
       </c>
-      <c r="C40" s="43">
+      <c r="C40" s="44">
         <f>(1-C43)*C39+C43*C42</f>
         <v/>
       </c>
@@ -10455,12 +10565,12 @@
           <t>Less non-controlling interests (reviewed 30 June 2026)</t>
         </is>
       </c>
-      <c r="B41" s="42">
-        <f>-Assumptions!$B$141</f>
-        <v/>
-      </c>
-      <c r="C41" s="43">
-        <f>(Assumptions!$B$120*Assumptions!$B$44+Assumptions!$B$121*(Assumptions!$B$43+0.03+Assumptions!$B$45)+Assumptions!$B$122*(Assumptions!$B$43+0.0435+Assumptions!$B$45)+Assumptions!$B$123*Assumptions!$B$44)/C44</f>
+      <c r="B41" s="43">
+        <f>-Assumptions!$B$142</f>
+        <v/>
+      </c>
+      <c r="C41" s="44">
+        <f>(Assumptions!$B$121*Assumptions!$B$45+Assumptions!$B$122*(Assumptions!$B$44+0.03+Assumptions!$B$46)+Assumptions!$B$123*(Assumptions!$B$44+0.0435+Assumptions!$B$46)+Assumptions!$B$124*Assumptions!$B$45)/C44</f>
         <v/>
       </c>
       <c r="E41" t="inlineStr">
@@ -10475,11 +10585,11 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B42" s="36">
+      <c r="B42" s="37">
         <f>B33+B40+B41</f>
         <v/>
       </c>
-      <c r="C42" s="41">
+      <c r="C42" s="42">
         <f>C41*(1-Assumptions!$B$8)</f>
         <v/>
       </c>
@@ -10495,11 +10605,11 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="B43" s="42">
+      <c r="B43" s="43">
         <f>Assumptions!$B$6-Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="C43" s="41">
+      <c r="C43" s="42">
         <f>C44/(C44+C45)</f>
         <v/>
       </c>
@@ -10520,7 +10630,7 @@
         <v/>
       </c>
       <c r="C44" s="17">
-        <f>Assumptions!$B$120+Assumptions!$B$121+Assumptions!$B$122+Assumptions!$B$123</f>
+        <f>Assumptions!$B$121+Assumptions!$B$122+Assumptions!$B$123+Assumptions!$B$124</f>
         <v/>
       </c>
       <c r="E44" t="inlineStr">
@@ -10542,7 +10652,7 @@
     </row>
     <row r="46">
       <c r="C46" s="8">
-        <f>(Assumptions!$B$121+Assumptions!$B$122)/C44</f>
+        <f>(Assumptions!$B$122+Assumptions!$B$123)/C44</f>
         <v/>
       </c>
       <c r="E46" t="inlineStr">
@@ -10552,8 +10662,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="C47" s="33">
-        <f>Assumptions!$B$10/(1+(1-Assumptions!$B$8)*C43/(1-C43))*(1+(1-Assumptions!$B$8)*Assumptions!$B$49/(1-Assumptions!$B$49))</f>
+      <c r="C47" s="34">
+        <f>Assumptions!$B$10/(1+(1-Assumptions!$B$8)*C43/(1-C43))*(1+(1-Assumptions!$B$8)*Assumptions!$B$50/(1-Assumptions!$B$50))</f>
         <v/>
       </c>
       <c r="E47" t="inlineStr">
@@ -10563,8 +10673,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="41">
-        <f>Assumptions!$B$47+C47*Assumptions!$B$48</f>
+      <c r="C48" s="42">
+        <f>Assumptions!$B$48+C47*Assumptions!$B$49</f>
         <v/>
       </c>
       <c r="E48" t="inlineStr">
@@ -10574,8 +10684,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="41">
-        <f>Assumptions!$B$46*(1-Assumptions!$B$8)</f>
+      <c r="C49" s="42">
+        <f>Assumptions!$B$47*(1-Assumptions!$B$8)</f>
         <v/>
       </c>
       <c r="E49" t="inlineStr">
@@ -10585,8 +10695,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="43">
-        <f>(1-Assumptions!$B$49)*C48+Assumptions!$B$49*C49</f>
+      <c r="C50" s="44">
+        <f>(1-Assumptions!$B$50)*C48+Assumptions!$B$50*C49</f>
         <v/>
       </c>
       <c r="E50" t="inlineStr">
@@ -10596,8 +10706,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="C51" s="41">
-        <f>Assumptions!$B$40+Assumptions!$B$10*Assumptions!$B$42</f>
+      <c r="C51" s="42">
+        <f>Assumptions!$B$41+Assumptions!$B$10*Assumptions!$B$43</f>
         <v/>
       </c>
       <c r="E51" t="inlineStr">
@@ -10648,8 +10758,8 @@
           <t>CIB facility rate — EGP corridor + 0.6%</t>
         </is>
       </c>
-      <c r="B56" s="41">
-        <f>Assumptions!$B$44</f>
+      <c r="B56" s="42">
+        <f>Assumptions!$B$45</f>
         <v/>
       </c>
     </row>
@@ -10659,8 +10769,8 @@
           <t>NBE/KfW facility rate — Euribor + 3.00%</t>
         </is>
       </c>
-      <c r="B57" s="41">
-        <f>Assumptions!$B$43+0.03</f>
+      <c r="B57" s="42">
+        <f>Assumptions!$B$44+0.03</f>
         <v/>
       </c>
     </row>
@@ -10670,8 +10780,8 @@
           <t>EBRD facility rate — Euribor + 4.35%</t>
         </is>
       </c>
-      <c r="B58" s="41">
-        <f>Assumptions!$B$43+0.0435</f>
+      <c r="B58" s="42">
+        <f>Assumptions!$B$44+0.0435</f>
         <v/>
       </c>
     </row>
@@ -10681,7 +10791,7 @@
           <t>ADOPTED blended cost of debt</t>
         </is>
       </c>
-      <c r="B59" s="43">
+      <c r="B59" s="44">
         <f>C41</f>
         <v/>
       </c>
@@ -10692,8 +10802,8 @@
           <t>Effective rate computed FY2024 (interest / average debt)</t>
         </is>
       </c>
-      <c r="B60" s="41">
-        <f>(Assumptions!$B$128+Assumptions!$B$129)/((Assumptions!$B$125+Assumptions!$B$124)/2)</f>
+      <c r="B60" s="42">
+        <f>(Assumptions!$B$129+Assumptions!$B$130)/((Assumptions!$B$126+Assumptions!$B$125)/2)</f>
         <v/>
       </c>
     </row>
@@ -10703,8 +10813,8 @@
           <t>Effective rate computed FY2025</t>
         </is>
       </c>
-      <c r="B61" s="41">
-        <f>(Assumptions!$B$126+Assumptions!$B$127)/((Assumptions!$B$124+C44-Assumptions!$B$123)/2)</f>
+      <c r="B61" s="42">
+        <f>(Assumptions!$B$127+Assumptions!$B$128)/((Assumptions!$B$125+C44-Assumptions!$B$124)/2)</f>
         <v/>
       </c>
     </row>
@@ -10714,8 +10824,8 @@
           <t>Effective rate computed Q1-2026, annualised</t>
         </is>
       </c>
-      <c r="B62" s="41">
-        <f>Assumptions!$B$150*4/((C44+Assumptions!$B$138)/2)</f>
+      <c r="B62" s="42">
+        <f>Assumptions!$B$151*4/((C44+Assumptions!$B$139)/2)</f>
         <v/>
       </c>
     </row>
@@ -10725,8 +10835,8 @@
           <t>Pound-EQUIVALENT cost of debt under interest parity</t>
         </is>
       </c>
-      <c r="B63" s="43">
-        <f>(Assumptions!$B$120*Assumptions!$B$44+Assumptions!$B$121*(Assumptions!$B$43+0.03+Assumptions!$B$45)+Assumptions!$B$122*(Assumptions!$B$43+0.0435+Assumptions!$B$45)+Assumptions!$B$123*Assumptions!$B$44)/C44</f>
+      <c r="B63" s="44">
+        <f>(Assumptions!$B$121*Assumptions!$B$45+Assumptions!$B$122*(Assumptions!$B$44+0.03+Assumptions!$B$46)+Assumptions!$B$123*(Assumptions!$B$44+0.0435+Assumptions!$B$46)+Assumptions!$B$124*Assumptions!$B$45)/C44</f>
         <v/>
       </c>
     </row>
@@ -10879,15 +10989,15 @@
         </is>
       </c>
       <c r="B5" s="14">
-        <f>Assumptions!$B$53</f>
+        <f>Assumptions!$B$54</f>
         <v/>
       </c>
       <c r="C5" s="14">
-        <f>Assumptions!$B$54</f>
+        <f>Assumptions!$B$55</f>
         <v/>
       </c>
       <c r="D5" s="14">
-        <f>Assumptions!$B$55</f>
+        <f>Assumptions!$B$56</f>
         <v/>
       </c>
       <c r="E5" s="14">
@@ -10918,15 +11028,15 @@
         </is>
       </c>
       <c r="B6" s="14">
-        <f>-Assumptions!$B$56</f>
+        <f>-Assumptions!$B$57</f>
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>-Assumptions!$B$57</f>
+        <f>-Assumptions!$B$58</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>-Assumptions!$B$58</f>
+        <f>-Assumptions!$B$59</f>
         <v/>
       </c>
       <c r="E6" s="17" t="n"/>
@@ -10980,15 +11090,15 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>-Assumptions!$B$59</f>
+        <f>-Assumptions!$B$60</f>
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>-Assumptions!$B$60</f>
+        <f>-Assumptions!$B$61</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>-Assumptions!$B$61</f>
+        <f>-Assumptions!$B$62</f>
         <v/>
       </c>
     </row>
@@ -10999,15 +11109,15 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>-Assumptions!$B$62-Assumptions!$B$65</f>
+        <f>-Assumptions!$B$63-Assumptions!$B$66</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>-Assumptions!$B$63-Assumptions!$B$66</f>
+        <f>-Assumptions!$B$64-Assumptions!$B$67</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>-Assumptions!$B$64-Assumptions!$B$67</f>
+        <f>-Assumptions!$B$65-Assumptions!$B$68</f>
         <v/>
       </c>
     </row>
@@ -11017,36 +11127,36 @@
           <t>OPERATING PROFIT</t>
         </is>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="37">
         <f>B7+B9+B10</f>
         <v/>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="37">
         <f>C7+C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="37">
         <f>D7+D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="36">
-        <f>E14-E13+Assumptions!$B$147*'Segments'!C60+Assumptions!$B$147*'Segments'!C61+Assumptions!$B$148*Assumptions!$C$29</f>
-        <v/>
-      </c>
-      <c r="F11" s="36">
-        <f>F14-F13+Assumptions!$B$147*'Segments'!D60+Assumptions!$B$147*'Segments'!D61+Assumptions!$B$148*Assumptions!$D$29</f>
-        <v/>
-      </c>
-      <c r="G11" s="36">
-        <f>G14-G13+Assumptions!$B$147*'Segments'!E60+Assumptions!$B$147*'Segments'!E61+Assumptions!$B$148*Assumptions!$E$29</f>
-        <v/>
-      </c>
-      <c r="H11" s="36">
-        <f>H14-H13+Assumptions!$B$147*'Segments'!F60+Assumptions!$B$147*'Segments'!F61+Assumptions!$B$148*Assumptions!$F$29</f>
-        <v/>
-      </c>
-      <c r="I11" s="36">
-        <f>I14-I13+Assumptions!$B$147*'Segments'!G60+Assumptions!$B$147*'Segments'!G61+Assumptions!$B$148*Assumptions!$G$29</f>
+      <c r="E11" s="37">
+        <f>E14-E13+Assumptions!$B$148*'Segments'!C60+Assumptions!$B$148*'Segments'!C61+Assumptions!$B$149*Assumptions!$C$30</f>
+        <v/>
+      </c>
+      <c r="F11" s="37">
+        <f>F14-F13+Assumptions!$B$148*'Segments'!D60+Assumptions!$B$148*'Segments'!D61+Assumptions!$B$149*Assumptions!$D$30</f>
+        <v/>
+      </c>
+      <c r="G11" s="37">
+        <f>G14-G13+Assumptions!$B$148*'Segments'!E60+Assumptions!$B$148*'Segments'!E61+Assumptions!$B$149*Assumptions!$E$30</f>
+        <v/>
+      </c>
+      <c r="H11" s="37">
+        <f>H14-H13+Assumptions!$B$148*'Segments'!F60+Assumptions!$B$148*'Segments'!F61+Assumptions!$B$149*Assumptions!$F$30</f>
+        <v/>
+      </c>
+      <c r="I11" s="37">
+        <f>I14-I13+Assumptions!$B$148*'Segments'!G60+Assumptions!$B$148*'Segments'!G61+Assumptions!$B$149*Assumptions!$G$30</f>
         <v/>
       </c>
     </row>
@@ -11096,15 +11206,15 @@
         </is>
       </c>
       <c r="B13" s="14">
-        <f>Assumptions!$B$80</f>
+        <f>Assumptions!$B$81</f>
         <v/>
       </c>
       <c r="C13" s="14">
-        <f>Assumptions!$B$81</f>
+        <f>Assumptions!$B$82</f>
         <v/>
       </c>
       <c r="D13" s="14">
-        <f>Assumptions!$B$82</f>
+        <f>Assumptions!$B$83</f>
         <v/>
       </c>
       <c r="E13" s="14">
@@ -11134,35 +11244,35 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="37">
         <f>B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="37">
         <f>C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="37">
         <f>D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>DCF!B7</f>
         <v/>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>DCF!C7</f>
         <v/>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="32">
         <f>DCF!D7</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="32">
         <f>DCF!E7</f>
         <v/>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="32">
         <f>DCF!F7</f>
         <v/>
       </c>
@@ -11213,35 +11323,35 @@
         </is>
       </c>
       <c r="B16" s="17">
-        <f>Assumptions!$B$68-B11</f>
+        <f>Assumptions!$B$69-B11</f>
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>Assumptions!$B$69-C11</f>
+        <f>Assumptions!$B$70-C11</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>Assumptions!$B$86+Assumptions!$B$87-Assumptions!$B$88+Assumptions!$B$89+1.14</f>
+        <f>Assumptions!$B$87+Assumptions!$B$88-Assumptions!$B$89+Assumptions!$B$90+1.14</f>
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>('Balance Sheet'!D9-Assumptions!$B$131)*Assumptions!$B$35-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$B$34-DCF!$C$44*DCF!$C$46*(Assumptions!$B$43+0.0435)</f>
+        <f>('Balance Sheet'!D9-Assumptions!$B$132)*Assumptions!$B$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$B$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$44+0.0435)</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>'Balance Sheet'!E9*Assumptions!$C$35-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$C$34-DCF!$C$44*DCF!$C$46*(Assumptions!$B$43+0.0435)</f>
+        <f>'Balance Sheet'!E9*Assumptions!$C$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$C$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$44+0.0435)</f>
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>'Balance Sheet'!F9*Assumptions!$D$35-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$D$34-DCF!$C$44*DCF!$C$46*(Assumptions!$B$43+0.0435)</f>
+        <f>'Balance Sheet'!F9*Assumptions!$D$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$D$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$44+0.0435)</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>'Balance Sheet'!G9*Assumptions!$E$35-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$E$34-DCF!$C$44*DCF!$C$46*(Assumptions!$B$43+0.0435)</f>
+        <f>'Balance Sheet'!G9*Assumptions!$E$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$E$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$44+0.0435)</f>
         <v/>
       </c>
       <c r="I16" s="17">
-        <f>'Balance Sheet'!H9*Assumptions!$F$35-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$F$34-DCF!$C$44*DCF!$C$46*(Assumptions!$B$43+0.0435)</f>
+        <f>'Balance Sheet'!H9*Assumptions!$F$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$F$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$44+0.0435)</f>
         <v/>
       </c>
     </row>
@@ -11252,15 +11362,15 @@
         </is>
       </c>
       <c r="B17" s="14">
-        <f>Assumptions!$B$68</f>
+        <f>Assumptions!$B$69</f>
         <v/>
       </c>
       <c r="C17" s="14">
-        <f>Assumptions!$B$69</f>
+        <f>Assumptions!$B$70</f>
         <v/>
       </c>
       <c r="D17" s="14">
-        <f>Assumptions!$B$70</f>
+        <f>Assumptions!$B$71</f>
         <v/>
       </c>
       <c r="E17" s="17">
@@ -11291,15 +11401,15 @@
         </is>
       </c>
       <c r="B18" s="14">
-        <f>-Assumptions!$B$71</f>
+        <f>-Assumptions!$B$72</f>
         <v/>
       </c>
       <c r="C18" s="14">
-        <f>-Assumptions!$B$72</f>
+        <f>-Assumptions!$B$73</f>
         <v/>
       </c>
       <c r="D18" s="14">
-        <f>-Assumptions!$B$73</f>
+        <f>-Assumptions!$B$74</f>
         <v/>
       </c>
       <c r="E18" s="17">
@@ -11368,35 +11478,35 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="B20" s="31">
-        <f>Assumptions!$B$74</f>
-        <v/>
-      </c>
-      <c r="C20" s="31">
+      <c r="B20" s="32">
         <f>Assumptions!$B$75</f>
         <v/>
       </c>
-      <c r="D20" s="31">
+      <c r="C20" s="32">
         <f>Assumptions!$B$76</f>
         <v/>
       </c>
-      <c r="E20" s="36">
+      <c r="D20" s="32">
+        <f>Assumptions!$B$77</f>
+        <v/>
+      </c>
+      <c r="E20" s="37">
         <f>E17+E18</f>
         <v/>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="37">
         <f>F17+F18</f>
         <v/>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="37">
         <f>G17+G18</f>
         <v/>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="37">
         <f>H17+H18</f>
         <v/>
       </c>
-      <c r="I20" s="36">
+      <c r="I20" s="37">
         <f>I17+I18</f>
         <v/>
       </c>
@@ -11408,15 +11518,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>Assumptions!$B$77</f>
+        <f>Assumptions!$B$78</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>Assumptions!$B$78</f>
+        <f>Assumptions!$B$79</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>Assumptions!$B$79</f>
+        <f>Assumptions!$B$80</f>
         <v/>
       </c>
       <c r="E21" s="13">
@@ -11447,31 +11557,31 @@
         </is>
       </c>
       <c r="C22" s="14">
+        <f>Assumptions!$B$133</f>
+        <v/>
+      </c>
+      <c r="D22" s="14">
         <f>Assumptions!$B$132</f>
         <v/>
       </c>
-      <c r="D22" s="14">
-        <f>Assumptions!$B$131</f>
-        <v/>
-      </c>
       <c r="E22" s="17">
-        <f>E20*Assumptions!$B$38</f>
+        <f>E20*Assumptions!$B$39</f>
         <v/>
       </c>
       <c r="F22" s="17">
-        <f>F20*Assumptions!$B$38</f>
+        <f>F20*Assumptions!$B$39</f>
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>G20*Assumptions!$B$38</f>
+        <f>G20*Assumptions!$B$39</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>H20*Assumptions!$B$38</f>
+        <f>H20*Assumptions!$B$39</f>
         <v/>
       </c>
       <c r="I22" s="17">
-        <f>I20*Assumptions!$B$38</f>
+        <f>I20*Assumptions!$B$39</f>
         <v/>
       </c>
     </row>
@@ -11516,7 +11626,7 @@
           <t>FY2025 check: components of non-operating income against the audited residual</t>
         </is>
       </c>
-      <c r="B24" s="42">
+      <c r="B24" s="43">
         <f>D16-(D17-D11)</f>
         <v/>
       </c>
